--- a/data/caiso_loads/raw/validation_data/historical-ems-hourly-load-for-november-2025.xlsx
+++ b/data/caiso_loads/raw/validation_data/historical-ems-hourly-load-for-november-2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr showInkAnnotation="0" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://records.oa.caiso.com/sites/MID/ID/RAP/Shared Documents/Records/Regulatory/CAISO/2025/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Brian\Documents\Coding\CAISO_load_forecasting\data\caiso_loads\raw\validation_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20000001_{3B4EFE0A-ADD5-44D0-9A15-8AAC99619139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B40D9CC-A128-40ED-B7E7-71B4AA6C5288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25185" yWindow="6330" windowWidth="23970" windowHeight="13470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="5175" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EMS Hourly Load for Nov 2025" sheetId="2" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Date</t>
   </si>
@@ -72,9 +72,6 @@
   </si>
   <si>
     <t>CAISO Public</t>
-  </si>
-  <si>
-    <t>Fall DST change occurs on 11/2/2025 at 1am</t>
   </si>
 </sst>
 </file>
@@ -479,12 +476,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:I724"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -506,11 +503,9 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I1" s="7"/>
+    </row>
+    <row r="2" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>45962</v>
       </c>
@@ -535,7 +530,7 @@
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>45962</v>
       </c>
@@ -560,7 +555,7 @@
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>45962</v>
       </c>
@@ -585,7 +580,7 @@
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>45962</v>
       </c>
@@ -608,7 +603,7 @@
         <v>20091.541722999998</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>45962</v>
       </c>
@@ -631,7 +626,7 @@
         <v>19716.6151289999</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>45962</v>
       </c>
@@ -654,7 +649,7 @@
         <v>20148.772381999999</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>45962</v>
       </c>
@@ -677,7 +672,7 @@
         <v>20857.173482999999</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>45962</v>
       </c>
@@ -700,7 +695,7 @@
         <v>21544.061919</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>45962</v>
       </c>
@@ -723,7 +718,7 @@
         <v>23152.606644</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>45962</v>
       </c>
@@ -746,7 +741,7 @@
         <v>25430.899081</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>45962</v>
       </c>
@@ -769,7 +764,7 @@
         <v>24598.039004999999</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>45962</v>
       </c>
@@ -792,7 +787,7 @@
         <v>23311.067046100001</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>45962</v>
       </c>
@@ -815,7 +810,7 @@
         <v>22806.918051299999</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>45962</v>
       </c>
@@ -838,7 +833,7 @@
         <v>23275.791327800001</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>45962</v>
       </c>
@@ -861,7 +856,7 @@
         <v>24753.803236</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>45962</v>
       </c>
@@ -884,7 +879,7 @@
         <v>25209.425478999899</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>45962</v>
       </c>
@@ -907,7 +902,7 @@
         <v>24053.291363</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>45962</v>
       </c>
@@ -930,7 +925,7 @@
         <v>25017.134429000002</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>45962</v>
       </c>
@@ -953,7 +948,7 @@
         <v>25920.934393999902</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>45962</v>
       </c>
@@ -976,7 +971,7 @@
         <v>25165.712566999999</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>45962</v>
       </c>
@@ -999,7 +994,7 @@
         <v>24258.944625999899</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>45962</v>
       </c>
@@ -1022,7 +1017,7 @@
         <v>23755.965345000001</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>45962</v>
       </c>
@@ -1045,7 +1040,7 @@
         <v>22957.283233999999</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>45962</v>
       </c>
@@ -1068,7 +1063,7 @@
         <v>21947.724784999999</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>45963</v>
       </c>
@@ -1091,7 +1086,7 @@
         <v>21286.208064999999</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>45963</v>
       </c>
@@ -1114,7 +1109,7 @@
         <v>20722.127034000001</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>45963</v>
       </c>
@@ -1137,7 +1132,7 @@
         <v>20529.902703</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>45963</v>
       </c>
@@ -1160,7 +1155,7 @@
         <v>19501.800663999999</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>45963</v>
       </c>
@@ -1183,7 +1178,7 @@
         <v>19008.376489999999</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>45963</v>
       </c>
@@ -1206,7 +1201,7 @@
         <v>18921.162972999999</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>45963</v>
       </c>
@@ -1229,7 +1224,7 @@
         <v>19137.3636679999</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>45963</v>
       </c>
@@ -1252,7 +1247,7 @@
         <v>19879.303474</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>45963</v>
       </c>
@@ -1275,7 +1270,7 @@
         <v>21529.409414999998</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>45963</v>
       </c>
@@ -1298,7 +1293,7 @@
         <v>24693.240489</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>45963</v>
       </c>
@@ -1321,7 +1316,7 @@
         <v>25148.760818999999</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>45963</v>
       </c>
@@ -1344,7 +1339,7 @@
         <v>25030.525387999998</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>45963</v>
       </c>
@@ -1367,7 +1362,7 @@
         <v>24391.065338</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>45963</v>
       </c>
@@ -1390,7 +1385,7 @@
         <v>23301.524715399999</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>45963</v>
       </c>
@@ -1413,7 +1408,7 @@
         <v>23258.404787200001</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>45963</v>
       </c>
@@ -1436,7 +1431,7 @@
         <v>23032.820176500001</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>45963</v>
       </c>
@@ -1459,7 +1454,7 @@
         <v>23079.385495999999</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>45963</v>
       </c>
@@ -1482,7 +1477,7 @@
         <v>24921.521510999999</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>45963</v>
       </c>
@@ -1505,7 +1500,7 @@
         <v>26132.320184</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>45963</v>
       </c>
@@ -1528,7 +1523,7 @@
         <v>25728.781652999998</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>45963</v>
       </c>
@@ -1551,7 +1546,7 @@
         <v>24941.5775709999</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>45963</v>
       </c>
@@ -1574,7 +1569,7 @@
         <v>24283.419076999999</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>45963</v>
       </c>
@@ -1597,7 +1592,7 @@
         <v>23613.461460999999</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>45963</v>
       </c>
@@ -1620,7 +1615,7 @@
         <v>22313.159239000001</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>45963</v>
       </c>
@@ -1643,7 +1638,7 @@
         <v>21237.401093</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>45964</v>
       </c>
@@ -1666,7 +1661,7 @@
         <v>20906.739388999998</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>45964</v>
       </c>
@@ -1689,7 +1684,7 @@
         <v>19890.383875</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>45964</v>
       </c>
@@ -1712,7 +1707,7 @@
         <v>20017.868299999998</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>45964</v>
       </c>
@@ -1735,7 +1730,7 @@
         <v>19524.22798</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <v>45964</v>
       </c>
@@ -1758,7 +1753,7 @@
         <v>19597.044266999899</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <v>45964</v>
       </c>
@@ -1781,7 +1776,7 @@
         <v>20922.442348</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <v>45964</v>
       </c>
@@ -1804,7 +1799,7 @@
         <v>22863.861138</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
         <v>45964</v>
       </c>
@@ -1827,7 +1822,7 @@
         <v>24510.364043000001</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
         <v>45964</v>
       </c>
@@ -1850,7 +1845,7 @@
         <v>27048.492050999899</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
         <v>45964</v>
       </c>
@@ -1873,7 +1868,7 @@
         <v>27019.148689000001</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
         <v>45964</v>
       </c>
@@ -1896,7 +1891,7 @@
         <v>26629.641482200001</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
         <v>45964</v>
       </c>
@@ -1919,7 +1914,7 @@
         <v>26688.879718</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
         <v>45964</v>
       </c>
@@ -1942,7 +1937,7 @@
         <v>27144.719776999998</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
         <v>45964</v>
       </c>
@@ -1965,7 +1960,7 @@
         <v>27339.415946000001</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
         <v>45964</v>
       </c>
@@ -1988,7 +1983,7 @@
         <v>27398.595508900002</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
         <v>45964</v>
       </c>
@@ -2011,7 +2006,7 @@
         <v>26214.490877</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
         <v>45964</v>
       </c>
@@ -2034,7 +2029,7 @@
         <v>27012.662206999899</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
         <v>45964</v>
       </c>
@@ -2057,7 +2052,7 @@
         <v>28030.780085999999</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
         <v>45964</v>
       </c>
@@ -2080,7 +2075,7 @@
         <v>27434.661069999998</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
         <v>45964</v>
       </c>
@@ -2103,7 +2098,7 @@
         <v>26409.521646000001</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
         <v>45964</v>
       </c>
@@ -2126,7 +2121,7 @@
         <v>25433.954924999998</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
         <v>45964</v>
       </c>
@@ -2149,7 +2144,7 @@
         <v>24771.759440000002</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
         <v>45964</v>
       </c>
@@ -2172,7 +2167,7 @@
         <v>23437.822667</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="3">
         <v>45964</v>
       </c>
@@ -2195,7 +2190,7 @@
         <v>22195.83381</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
         <v>45965</v>
       </c>
@@ -2218,7 +2213,7 @@
         <v>21757.928748999999</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
         <v>45965</v>
       </c>
@@ -2241,7 +2236,7 @@
         <v>20998.940747000001</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
         <v>45965</v>
       </c>
@@ -2264,7 +2259,7 @@
         <v>21035.482857999999</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
         <v>45965</v>
       </c>
@@ -2287,7 +2282,7 @@
         <v>20458.101535000002</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
         <v>45965</v>
       </c>
@@ -2310,7 +2305,7 @@
         <v>20496.596863999999</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
         <v>45965</v>
       </c>
@@ -2333,7 +2328,7 @@
         <v>21667.0868549999</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="3">
         <v>45965</v>
       </c>
@@ -2356,7 +2351,7 @@
         <v>23620.980571</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="3">
         <v>45965</v>
       </c>
@@ -2379,7 +2374,7 @@
         <v>25195.535960000001</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="3">
         <v>45965</v>
       </c>
@@ -2402,7 +2397,7 @@
         <v>27369.166000000001</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="3">
         <v>45965</v>
       </c>
@@ -2425,7 +2420,7 @@
         <v>27472.531326</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="3">
         <v>45965</v>
       </c>
@@ -2448,7 +2443,7 @@
         <v>27100.774168</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="3">
         <v>45965</v>
       </c>
@@ -2471,7 +2466,7 @@
         <v>26853.548043999999</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="3">
         <v>45965</v>
       </c>
@@ -2494,7 +2489,7 @@
         <v>27422.908240999899</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
         <v>45965</v>
       </c>
@@ -2517,7 +2512,7 @@
         <v>27142.066933999999</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
         <v>45965</v>
       </c>
@@ -2540,7 +2535,7 @@
         <v>26346.242301999999</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
         <v>45965</v>
       </c>
@@ -2563,7 +2558,7 @@
         <v>25907.116286</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="3">
         <v>45965</v>
       </c>
@@ -2586,7 +2581,7 @@
         <v>27032.816076999999</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="3">
         <v>45965</v>
       </c>
@@ -2609,7 +2604,7 @@
         <v>28233.476499</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="3">
         <v>45965</v>
       </c>
@@ -2632,7 +2627,7 @@
         <v>27817.5146949999</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="3">
         <v>45965</v>
       </c>
@@ -2655,7 +2650,7 @@
         <v>26525.849416999899</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="3">
         <v>45965</v>
       </c>
@@ -2678,7 +2673,7 @@
         <v>25553.870459000002</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="3">
         <v>45965</v>
       </c>
@@ -2701,7 +2696,7 @@
         <v>24940.9904509999</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="3">
         <v>45965</v>
       </c>
@@ -2724,7 +2719,7 @@
         <v>23559.857508999899</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="3">
         <v>45965</v>
       </c>
@@ -2747,7 +2742,7 @@
         <v>22288.5049</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="3">
         <v>45966</v>
       </c>
@@ -2770,7 +2765,7 @@
         <v>21724.163046999998</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="3">
         <v>45966</v>
       </c>
@@ -2793,7 +2788,7 @@
         <v>21023.675768000001</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="3">
         <v>45966</v>
       </c>
@@ -2816,7 +2811,7 @@
         <v>20395.289231999999</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="3">
         <v>45966</v>
       </c>
@@ -2839,7 +2834,7 @@
         <v>20361.738428000001</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="3">
         <v>45966</v>
       </c>
@@ -2862,7 +2857,7 @@
         <v>20381.126165000001</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="3">
         <v>45966</v>
       </c>
@@ -2885,7 +2880,7 @@
         <v>21581.775966000001</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="3">
         <v>45966</v>
       </c>
@@ -2908,7 +2903,7 @@
         <v>23415.781122</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="3">
         <v>45966</v>
       </c>
@@ -2931,7 +2926,7 @@
         <v>26046.936787999999</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="3">
         <v>45966</v>
       </c>
@@ -2954,7 +2949,7 @@
         <v>28443.256326999999</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="3">
         <v>45966</v>
       </c>
@@ -2977,7 +2972,7 @@
         <v>28318.464337000001</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="3">
         <v>45966</v>
       </c>
@@ -3000,7 +2995,7 @@
         <v>28302.598796999999</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="3">
         <v>45966</v>
       </c>
@@ -3023,7 +3018,7 @@
         <v>28588.381400999999</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="3">
         <v>45966</v>
       </c>
@@ -3046,7 +3041,7 @@
         <v>28254.165800999999</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="3">
         <v>45966</v>
       </c>
@@ -3069,7 +3064,7 @@
         <v>27937.227046</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="3">
         <v>45966</v>
       </c>
@@ -3092,7 +3087,7 @@
         <v>27190.946179999999</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="3">
         <v>45966</v>
       </c>
@@ -3115,7 +3110,7 @@
         <v>25721.315802999899</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="3">
         <v>45966</v>
       </c>
@@ -3138,7 +3133,7 @@
         <v>26355.077861000002</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="3">
         <v>45966</v>
       </c>
@@ -3161,7 +3156,7 @@
         <v>27299.611663</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="3">
         <v>45966</v>
       </c>
@@ -3184,7 +3179,7 @@
         <v>26917.5449669999</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="3">
         <v>45966</v>
       </c>
@@ -3207,7 +3202,7 @@
         <v>26383.194206</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="3">
         <v>45966</v>
       </c>
@@ -3230,7 +3225,7 @@
         <v>25743.035885000001</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="3">
         <v>45966</v>
       </c>
@@ -3253,7 +3248,7 @@
         <v>25217.584952000001</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="3">
         <v>45966</v>
       </c>
@@ -3276,7 +3271,7 @@
         <v>23851.117477</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="3">
         <v>45966</v>
       </c>
@@ -3299,7 +3294,7 @@
         <v>22600.164035000002</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="3">
         <v>45967</v>
       </c>
@@ -3322,7 +3317,7 @@
         <v>22142.178128</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="3">
         <v>45967</v>
       </c>
@@ -3345,7 +3340,7 @@
         <v>21249.371620000002</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="3">
         <v>45967</v>
       </c>
@@ -3368,7 +3363,7 @@
         <v>21078.946313</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="3">
         <v>45967</v>
       </c>
@@ -3391,7 +3386,7 @@
         <v>20851.7386669999</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="3">
         <v>45967</v>
       </c>
@@ -3414,7 +3409,7 @@
         <v>20759.959093000001</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="3">
         <v>45967</v>
       </c>
@@ -3437,7 +3432,7 @@
         <v>21903.051737000002</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="3">
         <v>45967</v>
       </c>
@@ -3460,7 +3455,7 @@
         <v>23660.782423000001</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="3">
         <v>45967</v>
       </c>
@@ -3483,7 +3478,7 @@
         <v>25458.212336000001</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="3">
         <v>45967</v>
       </c>
@@ -3506,7 +3501,7 @@
         <v>28596.253594000002</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="3">
         <v>45967</v>
       </c>
@@ -3529,7 +3524,7 @@
         <v>29548.655796999999</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="3">
         <v>45967</v>
       </c>
@@ -3552,7 +3547,7 @@
         <v>28282.200199999999</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="3">
         <v>45967</v>
       </c>
@@ -3575,7 +3570,7 @@
         <v>27073.276331100002</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="3">
         <v>45967</v>
       </c>
@@ -3598,7 +3593,7 @@
         <v>26871.0676958</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="3">
         <v>45967</v>
       </c>
@@ -3621,7 +3616,7 @@
         <v>27428.477263199999</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="3">
         <v>45967</v>
       </c>
@@ -3644,7 +3639,7 @@
         <v>26966.474427900001</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="3">
         <v>45967</v>
       </c>
@@ -3667,7 +3662,7 @@
         <v>25874.473509899999</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="3">
         <v>45967</v>
       </c>
@@ -3690,7 +3685,7 @@
         <v>26344.857470999999</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="3">
         <v>45967</v>
       </c>
@@ -3713,7 +3708,7 @@
         <v>27573.478498</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="3">
         <v>45967</v>
       </c>
@@ -3736,7 +3731,7 @@
         <v>26959.458761000002</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="3">
         <v>45967</v>
       </c>
@@ -3759,7 +3754,7 @@
         <v>26465.956074000002</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="3">
         <v>45967</v>
       </c>
@@ -3782,7 +3777,7 @@
         <v>25766.404826999998</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="3">
         <v>45967</v>
       </c>
@@ -3805,7 +3800,7 @@
         <v>24895.331564</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" s="3">
         <v>45967</v>
       </c>
@@ -3828,7 +3823,7 @@
         <v>24099.685105</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="3">
         <v>45967</v>
       </c>
@@ -3851,7 +3846,7 @@
         <v>23110.429982000001</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" s="3">
         <v>45968</v>
       </c>
@@ -3874,7 +3869,7 @@
         <v>22213.219043000001</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" s="3">
         <v>45968</v>
       </c>
@@ -3897,7 +3892,7 @@
         <v>21681.482497000001</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="3">
         <v>45968</v>
       </c>
@@ -3920,7 +3915,7 @@
         <v>21176.514178000001</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="3">
         <v>45968</v>
       </c>
@@ -3943,7 +3938,7 @@
         <v>21175.911620999999</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" s="3">
         <v>45968</v>
       </c>
@@ -3966,7 +3961,7 @@
         <v>20672.5142649999</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" s="3">
         <v>45968</v>
       </c>
@@ -3989,7 +3984,7 @@
         <v>21816.726074999999</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" s="3">
         <v>45968</v>
       </c>
@@ -4012,7 +4007,7 @@
         <v>23450.463949000001</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" s="3">
         <v>45968</v>
       </c>
@@ -4035,7 +4030,7 @@
         <v>25285.251703000002</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" s="3">
         <v>45968</v>
       </c>
@@ -4058,7 +4053,7 @@
         <v>27825.888533000001</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" s="3">
         <v>45968</v>
       </c>
@@ -4081,7 +4076,7 @@
         <v>28041.552516</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" s="3">
         <v>45968</v>
       </c>
@@ -4104,7 +4099,7 @@
         <v>27187.407708999999</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" s="3">
         <v>45968</v>
       </c>
@@ -4127,7 +4122,7 @@
         <v>27165.697923</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" s="3">
         <v>45968</v>
       </c>
@@ -4150,7 +4145,7 @@
         <v>28087.737965</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" s="3">
         <v>45968</v>
       </c>
@@ -4173,7 +4168,7 @@
         <v>29120.045402</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161" s="3">
         <v>45968</v>
       </c>
@@ -4196,7 +4191,7 @@
         <v>29214.248709</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" s="3">
         <v>45968</v>
       </c>
@@ -4219,7 +4214,7 @@
         <v>26957.022884999998</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" s="3">
         <v>45968</v>
       </c>
@@ -4242,7 +4237,7 @@
         <v>26999.314681999898</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" s="3">
         <v>45968</v>
       </c>
@@ -4265,7 +4260,7 @@
         <v>27724.095810999999</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" s="3">
         <v>45968</v>
       </c>
@@ -4288,7 +4283,7 @@
         <v>27043.753239000001</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166" s="3">
         <v>45968</v>
       </c>
@@ -4311,7 +4306,7 @@
         <v>26116.002585999999</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167" s="3">
         <v>45968</v>
       </c>
@@ -4334,7 +4329,7 @@
         <v>25251.139220999899</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168" s="3">
         <v>45968</v>
       </c>
@@ -4357,7 +4352,7 @@
         <v>24671.042394</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" s="3">
         <v>45968</v>
       </c>
@@ -4380,7 +4375,7 @@
         <v>23662.582824999899</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170" s="3">
         <v>45968</v>
       </c>
@@ -4403,7 +4398,7 @@
         <v>22564.465854999999</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" s="3">
         <v>45969</v>
       </c>
@@ -4426,7 +4421,7 @@
         <v>22333.716221999999</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172" s="3">
         <v>45969</v>
       </c>
@@ -4449,7 +4444,7 @@
         <v>21499.728504999999</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" s="3">
         <v>45969</v>
       </c>
@@ -4472,7 +4467,7 @@
         <v>20700.181065000001</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174" s="3">
         <v>45969</v>
       </c>
@@ -4495,7 +4490,7 @@
         <v>20451.160359000001</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175" s="3">
         <v>45969</v>
       </c>
@@ -4518,7 +4513,7 @@
         <v>20605.466832999999</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176" s="3">
         <v>45969</v>
       </c>
@@ -4541,7 +4536,7 @@
         <v>20867.698978</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" s="3">
         <v>45969</v>
       </c>
@@ -4564,7 +4559,7 @@
         <v>21720.071016000002</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178" s="3">
         <v>45969</v>
       </c>
@@ -4587,7 +4582,7 @@
         <v>22549.912980000001</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179" s="3">
         <v>45969</v>
       </c>
@@ -4610,7 +4605,7 @@
         <v>24295.471987999899</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180" s="3">
         <v>45969</v>
       </c>
@@ -4633,7 +4628,7 @@
         <v>25549.870707499998</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181" s="3">
         <v>45969</v>
       </c>
@@ -4656,7 +4651,7 @@
         <v>25034.302173799999</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182" s="3">
         <v>45969</v>
       </c>
@@ -4679,7 +4674,7 @@
         <v>24684.2327205</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183" s="3">
         <v>45969</v>
       </c>
@@ -4702,7 +4697,7 @@
         <v>25008.307223759999</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184" s="3">
         <v>45969</v>
       </c>
@@ -4725,7 +4720,7 @@
         <v>25950.5335291999</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185" s="3">
         <v>45969</v>
       </c>
@@ -4748,7 +4743,7 @@
         <v>25538.360990599998</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186" s="3">
         <v>45969</v>
       </c>
@@ -4771,7 +4766,7 @@
         <v>24626.08526</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187" s="3">
         <v>45969</v>
       </c>
@@ -4794,7 +4789,7 @@
         <v>25377.285992999899</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" s="3">
         <v>45969</v>
       </c>
@@ -4817,7 +4812,7 @@
         <v>26383.079621999899</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" s="3">
         <v>45969</v>
       </c>
@@ -4840,7 +4835,7 @@
         <v>25793.075977</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" s="3">
         <v>45969</v>
       </c>
@@ -4863,7 +4858,7 @@
         <v>25041.651679999999</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" s="3">
         <v>45969</v>
       </c>
@@ -4886,7 +4881,7 @@
         <v>24204.22363</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192" s="3">
         <v>45969</v>
       </c>
@@ -4909,7 +4904,7 @@
         <v>23729.190447999899</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193" s="3">
         <v>45969</v>
       </c>
@@ -4932,7 +4927,7 @@
         <v>22837.283149999999</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" s="3">
         <v>45969</v>
       </c>
@@ -4955,7 +4950,7 @@
         <v>21966.862234</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" s="3">
         <v>45970</v>
       </c>
@@ -4978,7 +4973,7 @@
         <v>21343.536358000001</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" s="3">
         <v>45970</v>
       </c>
@@ -5001,7 +4996,7 @@
         <v>20574.832977999999</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197" s="3">
         <v>45970</v>
       </c>
@@ -5024,7 +5019,7 @@
         <v>19971.859565999999</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198" s="3">
         <v>45970</v>
       </c>
@@ -5047,7 +5042,7 @@
         <v>19501.763004</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199" s="3">
         <v>45970</v>
       </c>
@@ -5070,7 +5065,7 @@
         <v>19456.620620000002</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200" s="3">
         <v>45970</v>
       </c>
@@ -5093,7 +5088,7 @@
         <v>19576.442611999999</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201" s="3">
         <v>45970</v>
       </c>
@@ -5116,7 +5111,7 @@
         <v>20203.152665000001</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202" s="3">
         <v>45970</v>
       </c>
@@ -5139,7 +5134,7 @@
         <v>21195.056101999999</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203" s="3">
         <v>45970</v>
       </c>
@@ -5162,7 +5157,7 @@
         <v>23336.672053800001</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204" s="3">
         <v>45970</v>
       </c>
@@ -5185,7 +5180,7 @@
         <v>24835.284230599998</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205" s="3">
         <v>45970</v>
       </c>
@@ -5208,7 +5203,7 @@
         <v>24226.8863376999</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206" s="3">
         <v>45970</v>
       </c>
@@ -5231,7 +5226,7 @@
         <v>24190.301849799998</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207" s="3">
         <v>45970</v>
       </c>
@@ -5254,7 +5249,7 @@
         <v>24960.971684299999</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208" s="3">
         <v>45970</v>
       </c>
@@ -5277,7 +5272,7 @@
         <v>25014.378438406999</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A209" s="3">
         <v>45970</v>
       </c>
@@ -5300,7 +5295,7 @@
         <v>25325.844051700002</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A210" s="3">
         <v>45970</v>
       </c>
@@ -5323,7 +5318,7 @@
         <v>25335.203969999999</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A211" s="3">
         <v>45970</v>
       </c>
@@ -5346,7 +5341,7 @@
         <v>26195.508049</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A212" s="3">
         <v>45970</v>
       </c>
@@ -5369,7 +5364,7 @@
         <v>26941.711422</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A213" s="3">
         <v>45970</v>
       </c>
@@ -5392,7 +5387,7 @@
         <v>26419.781846999998</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A214" s="3">
         <v>45970</v>
       </c>
@@ -5415,7 +5410,7 @@
         <v>25663.714381000002</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A215" s="3">
         <v>45970</v>
       </c>
@@ -5438,7 +5433,7 @@
         <v>25071.570723000001</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A216" s="3">
         <v>45970</v>
       </c>
@@ -5461,7 +5456,7 @@
         <v>24216.937622000001</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A217" s="3">
         <v>45970</v>
       </c>
@@ -5484,7 +5479,7 @@
         <v>23040.416406</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A218" s="3">
         <v>45970</v>
       </c>
@@ -5507,7 +5502,7 @@
         <v>21766.016069000001</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A219" s="3">
         <v>45971</v>
       </c>
@@ -5530,7 +5525,7 @@
         <v>21348.331405000001</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A220" s="3">
         <v>45971</v>
       </c>
@@ -5553,7 +5548,7 @@
         <v>20589.284972000001</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A221" s="3">
         <v>45971</v>
       </c>
@@ -5576,7 +5571,7 @@
         <v>20234.234012000001</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A222" s="3">
         <v>45971</v>
       </c>
@@ -5599,7 +5594,7 @@
         <v>20134.240674000001</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A223" s="3">
         <v>45971</v>
       </c>
@@ -5622,7 +5617,7 @@
         <v>20312.767949000001</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A224" s="3">
         <v>45971</v>
       </c>
@@ -5645,7 +5640,7 @@
         <v>21406.711966999999</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225" s="3">
         <v>45971</v>
       </c>
@@ -5668,7 +5663,7 @@
         <v>22919.8772939999</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A226" s="3">
         <v>45971</v>
       </c>
@@ -5691,7 +5686,7 @@
         <v>25404.462790000001</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A227" s="3">
         <v>45971</v>
       </c>
@@ -5714,7 +5709,7 @@
         <v>28825.679768999998</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A228" s="3">
         <v>45971</v>
       </c>
@@ -5737,7 +5732,7 @@
         <v>29413.433754999998</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A229" s="3">
         <v>45971</v>
       </c>
@@ -5760,7 +5755,7 @@
         <v>29029.127321</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A230" s="3">
         <v>45971</v>
       </c>
@@ -5783,7 +5778,7 @@
         <v>28100.116973</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A231" s="3">
         <v>45971</v>
       </c>
@@ -5806,7 +5801,7 @@
         <v>28271.038417</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A232" s="3">
         <v>45971</v>
       </c>
@@ -5829,7 +5824,7 @@
         <v>28340.473677999998</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A233" s="3">
         <v>45971</v>
       </c>
@@ -5852,7 +5847,7 @@
         <v>29090.322961999998</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A234" s="3">
         <v>45971</v>
       </c>
@@ -5875,7 +5870,7 @@
         <v>29043.267850999899</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A235" s="3">
         <v>45971</v>
       </c>
@@ -5898,7 +5893,7 @@
         <v>29405.485795000001</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A236" s="3">
         <v>45971</v>
       </c>
@@ -5921,7 +5916,7 @@
         <v>29609.903648</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A237" s="3">
         <v>45971</v>
       </c>
@@ -5944,7 +5939,7 @@
         <v>28654.5865649999</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A238" s="3">
         <v>45971</v>
       </c>
@@ -5967,7 +5962,7 @@
         <v>27584.261444</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A239" s="3">
         <v>45971</v>
       </c>
@@ -5990,7 +5985,7 @@
         <v>26867.986535</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A240" s="3">
         <v>45971</v>
       </c>
@@ -6013,7 +6008,7 @@
         <v>26040.818965999999</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A241" s="3">
         <v>45971</v>
       </c>
@@ -6036,7 +6031,7 @@
         <v>24723.828304999999</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A242" s="3">
         <v>45971</v>
       </c>
@@ -6059,7 +6054,7 @@
         <v>23140.893979</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A243" s="3">
         <v>45972</v>
       </c>
@@ -6082,7 +6077,7 @@
         <v>22373.85514</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A244" s="3">
         <v>45972</v>
       </c>
@@ -6105,7 +6100,7 @@
         <v>21345.004800999999</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A245" s="3">
         <v>45972</v>
       </c>
@@ -6128,7 +6123,7 @@
         <v>20877.3182539999</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A246" s="3">
         <v>45972</v>
       </c>
@@ -6151,7 +6146,7 @@
         <v>20476.22754</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A247" s="3">
         <v>45972</v>
       </c>
@@ -6174,7 +6169,7 @@
         <v>20575.620456000001</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A248" s="3">
         <v>45972</v>
       </c>
@@ -6197,7 +6192,7 @@
         <v>21448.745772999999</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A249" s="3">
         <v>45972</v>
       </c>
@@ -6220,7 +6215,7 @@
         <v>22919.122329000002</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A250" s="3">
         <v>45972</v>
       </c>
@@ -6243,7 +6238,7 @@
         <v>25663.892562999899</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A251" s="3">
         <v>45972</v>
       </c>
@@ -6266,7 +6261,7 @@
         <v>28070.914554999999</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A252" s="3">
         <v>45972</v>
       </c>
@@ -6289,7 +6284,7 @@
         <v>28534.962965999999</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A253" s="3">
         <v>45972</v>
       </c>
@@ -6312,7 +6307,7 @@
         <v>28531.071131000001</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A254" s="3">
         <v>45972</v>
       </c>
@@ -6335,7 +6330,7 @@
         <v>28358.407745</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A255" s="3">
         <v>45972</v>
       </c>
@@ -6358,7 +6353,7 @@
         <v>27443.518233999999</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A256" s="3">
         <v>45972</v>
       </c>
@@ -6381,7 +6376,7 @@
         <v>27168.521784</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A257" s="3">
         <v>45972</v>
       </c>
@@ -6404,7 +6399,7 @@
         <v>27328.685292999999</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A258" s="3">
         <v>45972</v>
       </c>
@@ -6427,7 +6422,7 @@
         <v>26786.710720999999</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A259" s="3">
         <v>45972</v>
       </c>
@@ -6450,7 +6445,7 @@
         <v>27372.877732000001</v>
       </c>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A260" s="3">
         <v>45972</v>
       </c>
@@ -6473,7 +6468,7 @@
         <v>28287.117974000001</v>
       </c>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A261" s="3">
         <v>45972</v>
       </c>
@@ -6496,7 +6491,7 @@
         <v>27708.997469999998</v>
       </c>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A262" s="3">
         <v>45972</v>
       </c>
@@ -6519,7 +6514,7 @@
         <v>27197.524840999999</v>
       </c>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A263" s="3">
         <v>45972</v>
       </c>
@@ -6542,7 +6537,7 @@
         <v>26381.752159</v>
       </c>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A264" s="3">
         <v>45972</v>
       </c>
@@ -6565,7 +6560,7 @@
         <v>25552.530589999998</v>
       </c>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A265" s="3">
         <v>45972</v>
       </c>
@@ -6588,7 +6583,7 @@
         <v>24233.699358000002</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A266" s="3">
         <v>45972</v>
       </c>
@@ -6611,7 +6606,7 @@
         <v>22878.818827999999</v>
       </c>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A267" s="3">
         <v>45973</v>
       </c>
@@ -6634,7 +6629,7 @@
         <v>22299.387349999899</v>
       </c>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A268" s="3">
         <v>45973</v>
       </c>
@@ -6657,7 +6652,7 @@
         <v>21750.048091000001</v>
       </c>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A269" s="3">
         <v>45973</v>
       </c>
@@ -6680,7 +6675,7 @@
         <v>21473.312568000001</v>
       </c>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A270" s="3">
         <v>45973</v>
       </c>
@@ -6703,7 +6698,7 @@
         <v>21261.928699</v>
       </c>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A271" s="3">
         <v>45973</v>
       </c>
@@ -6726,7 +6721,7 @@
         <v>20931.21326</v>
       </c>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A272" s="3">
         <v>45973</v>
       </c>
@@ -6749,7 +6744,7 @@
         <v>21934.447441</v>
       </c>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A273" s="3">
         <v>45973</v>
       </c>
@@ -6772,7 +6767,7 @@
         <v>23510.423301999999</v>
       </c>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A274" s="3">
         <v>45973</v>
       </c>
@@ -6795,7 +6790,7 @@
         <v>24863.005621</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A275" s="3">
         <v>45973</v>
       </c>
@@ -6818,7 +6813,7 @@
         <v>26638.750693999998</v>
       </c>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A276" s="3">
         <v>45973</v>
       </c>
@@ -6841,7 +6836,7 @@
         <v>27224.651594999999</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A277" s="3">
         <v>45973</v>
       </c>
@@ -6864,7 +6859,7 @@
         <v>27711.536703999998</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A278" s="3">
         <v>45973</v>
       </c>
@@ -6887,7 +6882,7 @@
         <v>28810.056442999899</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A279" s="3">
         <v>45973</v>
       </c>
@@ -6910,7 +6905,7 @@
         <v>29033.526688999998</v>
       </c>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A280" s="3">
         <v>45973</v>
       </c>
@@ -6933,7 +6928,7 @@
         <v>28056.051985999999</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A281" s="3">
         <v>45973</v>
       </c>
@@ -6956,7 +6951,7 @@
         <v>27135.852534000001</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A282" s="3">
         <v>45973</v>
       </c>
@@ -6979,7 +6974,7 @@
         <v>26954.567732</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A283" s="3">
         <v>45973</v>
       </c>
@@ -7002,7 +6997,7 @@
         <v>27353.700826</v>
       </c>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A284" s="3">
         <v>45973</v>
       </c>
@@ -7025,7 +7020,7 @@
         <v>28375.598696999899</v>
       </c>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A285" s="3">
         <v>45973</v>
       </c>
@@ -7048,7 +7043,7 @@
         <v>27533.584361000001</v>
       </c>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A286" s="3">
         <v>45973</v>
       </c>
@@ -7071,7 +7066,7 @@
         <v>26958.297677999999</v>
       </c>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A287" s="3">
         <v>45973</v>
       </c>
@@ -7094,7 +7089,7 @@
         <v>25867.749485999899</v>
       </c>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A288" s="3">
         <v>45973</v>
       </c>
@@ -7117,7 +7112,7 @@
         <v>25138.134058</v>
       </c>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A289" s="3">
         <v>45973</v>
       </c>
@@ -7140,7 +7135,7 @@
         <v>24075.3138159999</v>
       </c>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A290" s="3">
         <v>45973</v>
       </c>
@@ -7163,7 +7158,7 @@
         <v>22870.825378000001</v>
       </c>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A291" s="3">
         <v>45974</v>
       </c>
@@ -7186,7 +7181,7 @@
         <v>21728.916926000002</v>
       </c>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A292" s="3">
         <v>45974</v>
       </c>
@@ -7209,7 +7204,7 @@
         <v>21083.396245</v>
       </c>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A293" s="3">
         <v>45974</v>
       </c>
@@ -7232,7 +7227,7 @@
         <v>20435.536678</v>
       </c>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A294" s="3">
         <v>45974</v>
       </c>
@@ -7255,7 +7250,7 @@
         <v>20304.765561</v>
       </c>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A295" s="3">
         <v>45974</v>
       </c>
@@ -7278,7 +7273,7 @@
         <v>20374.807554999999</v>
       </c>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A296" s="3">
         <v>45974</v>
       </c>
@@ -7301,7 +7296,7 @@
         <v>21283.786925</v>
       </c>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A297" s="3">
         <v>45974</v>
       </c>
@@ -7324,7 +7319,7 @@
         <v>22891.802528</v>
       </c>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A298" s="3">
         <v>45974</v>
       </c>
@@ -7347,7 +7342,7 @@
         <v>24910.694657</v>
       </c>
     </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A299" s="3">
         <v>45974</v>
       </c>
@@ -7370,7 +7365,7 @@
         <v>28515.4756209999</v>
       </c>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A300" s="3">
         <v>45974</v>
       </c>
@@ -7393,7 +7388,7 @@
         <v>30023.096051</v>
       </c>
     </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A301" s="3">
         <v>45974</v>
       </c>
@@ -7416,7 +7411,7 @@
         <v>29771.147493</v>
       </c>
     </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A302" s="3">
         <v>45974</v>
       </c>
@@ -7439,7 +7434,7 @@
         <v>29748.635656999999</v>
       </c>
     </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A303" s="3">
         <v>45974</v>
       </c>
@@ -7462,7 +7457,7 @@
         <v>28956.226052999999</v>
       </c>
     </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A304" s="3">
         <v>45974</v>
       </c>
@@ -7485,7 +7480,7 @@
         <v>27852.236922</v>
       </c>
     </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A305" s="3">
         <v>45974</v>
       </c>
@@ -7508,7 +7503,7 @@
         <v>26800.815214999999</v>
       </c>
     </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A306" s="3">
         <v>45974</v>
       </c>
@@ -7531,7 +7526,7 @@
         <v>26620.797315</v>
       </c>
     </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A307" s="3">
         <v>45974</v>
       </c>
@@ -7554,7 +7549,7 @@
         <v>26509.793451000001</v>
       </c>
     </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A308" s="3">
         <v>45974</v>
       </c>
@@ -7577,7 +7572,7 @@
         <v>27241.790270000001</v>
       </c>
     </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A309" s="3">
         <v>45974</v>
       </c>
@@ -7600,7 +7595,7 @@
         <v>26765.126939000002</v>
       </c>
     </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A310" s="3">
         <v>45974</v>
       </c>
@@ -7623,7 +7618,7 @@
         <v>26089.297047</v>
       </c>
     </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A311" s="3">
         <v>45974</v>
       </c>
@@ -7646,7 +7641,7 @@
         <v>25628.296131999999</v>
       </c>
     </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A312" s="3">
         <v>45974</v>
       </c>
@@ -7669,7 +7664,7 @@
         <v>24967.164287</v>
       </c>
     </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A313" s="3">
         <v>45974</v>
       </c>
@@ -7692,7 +7687,7 @@
         <v>23750.127274999999</v>
       </c>
     </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A314" s="3">
         <v>45974</v>
       </c>
@@ -7715,7 +7710,7 @@
         <v>22434.025313999999</v>
       </c>
     </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A315" s="3">
         <v>45975</v>
       </c>
@@ -7738,7 +7733,7 @@
         <v>22578.572271000001</v>
       </c>
     </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A316" s="3">
         <v>45975</v>
       </c>
@@ -7761,7 +7756,7 @@
         <v>22128.497170999999</v>
       </c>
     </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A317" s="3">
         <v>45975</v>
       </c>
@@ -7784,7 +7779,7 @@
         <v>22079.970166999999</v>
       </c>
     </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A318" s="3">
         <v>45975</v>
       </c>
@@ -7807,7 +7802,7 @@
         <v>21601.934732999998</v>
       </c>
     </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A319" s="3">
         <v>45975</v>
       </c>
@@ -7830,7 +7825,7 @@
         <v>21113.309456999999</v>
       </c>
     </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A320" s="3">
         <v>45975</v>
       </c>
@@ -7853,7 +7848,7 @@
         <v>22097.445672999998</v>
       </c>
     </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A321" s="3">
         <v>45975</v>
       </c>
@@ -7876,7 +7871,7 @@
         <v>22806.021892999899</v>
       </c>
     </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A322" s="3">
         <v>45975</v>
       </c>
@@ -7899,7 +7894,7 @@
         <v>24356.631012999998</v>
       </c>
     </row>
-    <row r="323" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A323" s="3">
         <v>45975</v>
       </c>
@@ -7922,7 +7917,7 @@
         <v>25257.155194999999</v>
       </c>
     </row>
-    <row r="324" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A324" s="3">
         <v>45975</v>
       </c>
@@ -7945,7 +7940,7 @@
         <v>25791.171773999999</v>
       </c>
     </row>
-    <row r="325" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A325" s="3">
         <v>45975</v>
       </c>
@@ -7968,7 +7963,7 @@
         <v>26472.327092</v>
       </c>
     </row>
-    <row r="326" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A326" s="3">
         <v>45975</v>
       </c>
@@ -7991,7 +7986,7 @@
         <v>26703.0482549999</v>
       </c>
     </row>
-    <row r="327" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A327" s="3">
         <v>45975</v>
       </c>
@@ -8014,7 +8009,7 @@
         <v>26927.180172</v>
       </c>
     </row>
-    <row r="328" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A328" s="3">
         <v>45975</v>
       </c>
@@ -8037,7 +8032,7 @@
         <v>26879.189813000001</v>
       </c>
     </row>
-    <row r="329" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A329" s="3">
         <v>45975</v>
       </c>
@@ -8060,7 +8055,7 @@
         <v>25782.854904</v>
       </c>
     </row>
-    <row r="330" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A330" s="3">
         <v>45975</v>
       </c>
@@ -8083,7 +8078,7 @@
         <v>25287.7855099999</v>
       </c>
     </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A331" s="3">
         <v>45975</v>
       </c>
@@ -8106,7 +8101,7 @@
         <v>25216.5447629999</v>
       </c>
     </row>
-    <row r="332" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A332" s="3">
         <v>45975</v>
       </c>
@@ -8129,7 +8124,7 @@
         <v>26300.485364</v>
       </c>
     </row>
-    <row r="333" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A333" s="3">
         <v>45975</v>
       </c>
@@ -8152,7 +8147,7 @@
         <v>25720.5018849999</v>
       </c>
     </row>
-    <row r="334" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A334" s="3">
         <v>45975</v>
       </c>
@@ -8175,7 +8170,7 @@
         <v>25720.206005</v>
       </c>
     </row>
-    <row r="335" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A335" s="3">
         <v>45975</v>
       </c>
@@ -8198,7 +8193,7 @@
         <v>25299.5059369999</v>
       </c>
     </row>
-    <row r="336" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A336" s="3">
         <v>45975</v>
       </c>
@@ -8221,7 +8216,7 @@
         <v>24413.186508999999</v>
       </c>
     </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A337" s="3">
         <v>45975</v>
       </c>
@@ -8244,7 +8239,7 @@
         <v>23333.467502</v>
       </c>
     </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A338" s="3">
         <v>45975</v>
       </c>
@@ -8267,7 +8262,7 @@
         <v>22464.712026000001</v>
       </c>
     </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A339" s="3">
         <v>45976</v>
       </c>
@@ -8290,7 +8285,7 @@
         <v>22197.353337</v>
       </c>
     </row>
-    <row r="340" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A340" s="3">
         <v>45976</v>
       </c>
@@ -8313,7 +8308,7 @@
         <v>21773.875694999999</v>
       </c>
     </row>
-    <row r="341" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A341" s="3">
         <v>45976</v>
       </c>
@@ -8336,7 +8331,7 @@
         <v>21802.260407000002</v>
       </c>
     </row>
-    <row r="342" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A342" s="3">
         <v>45976</v>
       </c>
@@ -8359,7 +8354,7 @@
         <v>21827.427786</v>
       </c>
     </row>
-    <row r="343" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A343" s="3">
         <v>45976</v>
       </c>
@@ -8382,7 +8377,7 @@
         <v>21514.8798939999</v>
       </c>
     </row>
-    <row r="344" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A344" s="3">
         <v>45976</v>
       </c>
@@ -8405,7 +8400,7 @@
         <v>21081.229324</v>
       </c>
     </row>
-    <row r="345" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A345" s="3">
         <v>45976</v>
       </c>
@@ -8428,7 +8423,7 @@
         <v>21314.340510000002</v>
       </c>
     </row>
-    <row r="346" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A346" s="3">
         <v>45976</v>
       </c>
@@ -8451,7 +8446,7 @@
         <v>21696.478657</v>
       </c>
     </row>
-    <row r="347" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A347" s="3">
         <v>45976</v>
       </c>
@@ -8474,7 +8469,7 @@
         <v>22707.019479999999</v>
       </c>
     </row>
-    <row r="348" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A348" s="3">
         <v>45976</v>
       </c>
@@ -8497,7 +8492,7 @@
         <v>23249.2412889999</v>
       </c>
     </row>
-    <row r="349" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A349" s="3">
         <v>45976</v>
       </c>
@@ -8520,7 +8515,7 @@
         <v>23422.266765</v>
       </c>
     </row>
-    <row r="350" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A350" s="3">
         <v>45976</v>
       </c>
@@ -8543,7 +8538,7 @@
         <v>23238.7958689999</v>
       </c>
     </row>
-    <row r="351" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A351" s="3">
         <v>45976</v>
       </c>
@@ -8566,7 +8561,7 @@
         <v>23186.457270999999</v>
       </c>
     </row>
-    <row r="352" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A352" s="3">
         <v>45976</v>
       </c>
@@ -8589,7 +8584,7 @@
         <v>23241.232216999899</v>
       </c>
     </row>
-    <row r="353" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A353" s="3">
         <v>45976</v>
       </c>
@@ -8612,7 +8607,7 @@
         <v>23270.5496519999</v>
       </c>
     </row>
-    <row r="354" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A354" s="3">
         <v>45976</v>
       </c>
@@ -8635,7 +8630,7 @@
         <v>23561.119691</v>
       </c>
     </row>
-    <row r="355" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A355" s="3">
         <v>45976</v>
       </c>
@@ -8658,7 +8653,7 @@
         <v>24329.021668000001</v>
       </c>
     </row>
-    <row r="356" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A356" s="3">
         <v>45976</v>
       </c>
@@ -8681,7 +8676,7 @@
         <v>24664.765932999999</v>
       </c>
     </row>
-    <row r="357" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A357" s="3">
         <v>45976</v>
       </c>
@@ -8704,7 +8699,7 @@
         <v>24321.321134999998</v>
       </c>
     </row>
-    <row r="358" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A358" s="3">
         <v>45976</v>
       </c>
@@ -8727,7 +8722,7 @@
         <v>23815.601236999999</v>
       </c>
     </row>
-    <row r="359" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A359" s="3">
         <v>45976</v>
       </c>
@@ -8750,7 +8745,7 @@
         <v>23459.454013999999</v>
       </c>
     </row>
-    <row r="360" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A360" s="3">
         <v>45976</v>
       </c>
@@ -8773,7 +8768,7 @@
         <v>22996.127412000002</v>
       </c>
     </row>
-    <row r="361" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A361" s="3">
         <v>45976</v>
       </c>
@@ -8796,7 +8791,7 @@
         <v>22709.093918999999</v>
       </c>
     </row>
-    <row r="362" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A362" s="3">
         <v>45976</v>
       </c>
@@ -8819,7 +8814,7 @@
         <v>21571.762933999998</v>
       </c>
     </row>
-    <row r="363" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A363" s="3">
         <v>45977</v>
       </c>
@@ -8842,7 +8837,7 @@
         <v>20932.586277999999</v>
       </c>
     </row>
-    <row r="364" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A364" s="3">
         <v>45977</v>
       </c>
@@ -8865,7 +8860,7 @@
         <v>19970.714951999998</v>
       </c>
     </row>
-    <row r="365" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A365" s="3">
         <v>45977</v>
       </c>
@@ -8888,7 +8883,7 @@
         <v>19365.462292</v>
       </c>
     </row>
-    <row r="366" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A366" s="3">
         <v>45977</v>
       </c>
@@ -8911,7 +8906,7 @@
         <v>18984.184448</v>
       </c>
     </row>
-    <row r="367" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A367" s="3">
         <v>45977</v>
       </c>
@@ -8934,7 +8929,7 @@
         <v>18864.350651000001</v>
       </c>
     </row>
-    <row r="368" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A368" s="3">
         <v>45977</v>
       </c>
@@ -8957,7 +8952,7 @@
         <v>19150.069565999998</v>
       </c>
     </row>
-    <row r="369" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A369" s="3">
         <v>45977</v>
       </c>
@@ -8980,7 +8975,7 @@
         <v>19537.968401999999</v>
       </c>
     </row>
-    <row r="370" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A370" s="3">
         <v>45977</v>
       </c>
@@ -9003,7 +8998,7 @@
         <v>20467.681651999999</v>
       </c>
     </row>
-    <row r="371" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A371" s="3">
         <v>45977</v>
       </c>
@@ -9026,7 +9021,7 @@
         <v>22473.544447</v>
       </c>
     </row>
-    <row r="372" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A372" s="3">
         <v>45977</v>
       </c>
@@ -9049,7 +9044,7 @@
         <v>23277.017374999999</v>
       </c>
     </row>
-    <row r="373" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A373" s="3">
         <v>45977</v>
       </c>
@@ -9072,7 +9067,7 @@
         <v>25064.834511999899</v>
       </c>
     </row>
-    <row r="374" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A374" s="3">
         <v>45977</v>
       </c>
@@ -9095,7 +9090,7 @@
         <v>25336.388411</v>
       </c>
     </row>
-    <row r="375" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A375" s="3">
         <v>45977</v>
       </c>
@@ -9118,7 +9113,7 @@
         <v>25230.155194999999</v>
       </c>
     </row>
-    <row r="376" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A376" s="3">
         <v>45977</v>
       </c>
@@ -9141,7 +9136,7 @@
         <v>24584.228499000001</v>
       </c>
     </row>
-    <row r="377" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A377" s="3">
         <v>45977</v>
       </c>
@@ -9164,7 +9159,7 @@
         <v>24325.69126</v>
       </c>
     </row>
-    <row r="378" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A378" s="3">
         <v>45977</v>
       </c>
@@ -9187,7 +9182,7 @@
         <v>22969.558256</v>
       </c>
     </row>
-    <row r="379" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A379" s="3">
         <v>45977</v>
       </c>
@@ -9210,7 +9205,7 @@
         <v>23397.697413999998</v>
       </c>
     </row>
-    <row r="380" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A380" s="3">
         <v>45977</v>
       </c>
@@ -9233,7 +9228,7 @@
         <v>24761.373697999999</v>
       </c>
     </row>
-    <row r="381" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A381" s="3">
         <v>45977</v>
       </c>
@@ -9256,7 +9251,7 @@
         <v>24544.264219000001</v>
       </c>
     </row>
-    <row r="382" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A382" s="3">
         <v>45977</v>
       </c>
@@ -9279,7 +9274,7 @@
         <v>24152.749755000001</v>
       </c>
     </row>
-    <row r="383" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A383" s="3">
         <v>45977</v>
       </c>
@@ -9302,7 +9297,7 @@
         <v>23659.058865999999</v>
       </c>
     </row>
-    <row r="384" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A384" s="3">
         <v>45977</v>
       </c>
@@ -9325,7 +9320,7 @@
         <v>23064.122598000002</v>
       </c>
     </row>
-    <row r="385" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A385" s="3">
         <v>45977</v>
       </c>
@@ -9348,7 +9343,7 @@
         <v>21957.821956</v>
       </c>
     </row>
-    <row r="386" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A386" s="3">
         <v>45977</v>
       </c>
@@ -9371,7 +9366,7 @@
         <v>21201.275796999998</v>
       </c>
     </row>
-    <row r="387" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A387" s="3">
         <v>45978</v>
       </c>
@@ -9394,7 +9389,7 @@
         <v>21989.867281999999</v>
       </c>
     </row>
-    <row r="388" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A388" s="3">
         <v>45978</v>
       </c>
@@ -9417,7 +9412,7 @@
         <v>21849.515013</v>
       </c>
     </row>
-    <row r="389" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A389" s="3">
         <v>45978</v>
       </c>
@@ -9440,7 +9435,7 @@
         <v>21041.268878999999</v>
       </c>
     </row>
-    <row r="390" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A390" s="3">
         <v>45978</v>
       </c>
@@ -9463,7 +9458,7 @@
         <v>20640.929156999999</v>
       </c>
     </row>
-    <row r="391" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A391" s="3">
         <v>45978</v>
       </c>
@@ -9486,7 +9481,7 @@
         <v>20560.976306</v>
       </c>
     </row>
-    <row r="392" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A392" s="3">
         <v>45978</v>
       </c>
@@ -9509,7 +9504,7 @@
         <v>21133.529519</v>
       </c>
     </row>
-    <row r="393" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A393" s="3">
         <v>45978</v>
       </c>
@@ -9532,7 +9527,7 @@
         <v>22574.704733999999</v>
       </c>
     </row>
-    <row r="394" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A394" s="3">
         <v>45978</v>
       </c>
@@ -9555,7 +9550,7 @@
         <v>24245.425943999999</v>
       </c>
     </row>
-    <row r="395" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A395" s="3">
         <v>45978</v>
       </c>
@@ -9578,7 +9573,7 @@
         <v>26421.432256</v>
       </c>
     </row>
-    <row r="396" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A396" s="3">
         <v>45978</v>
       </c>
@@ -9601,7 +9596,7 @@
         <v>26884.527564</v>
       </c>
     </row>
-    <row r="397" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A397" s="3">
         <v>45978</v>
       </c>
@@ -9624,7 +9619,7 @@
         <v>26479.873962999998</v>
       </c>
     </row>
-    <row r="398" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A398" s="3">
         <v>45978</v>
       </c>
@@ -9647,7 +9642,7 @@
         <v>26303.123084999999</v>
       </c>
     </row>
-    <row r="399" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A399" s="3">
         <v>45978</v>
       </c>
@@ -9670,7 +9665,7 @@
         <v>26684.324682999999</v>
       </c>
     </row>
-    <row r="400" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A400" s="3">
         <v>45978</v>
       </c>
@@ -9693,7 +9688,7 @@
         <v>25599.79262</v>
       </c>
     </row>
-    <row r="401" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A401" s="3">
         <v>45978</v>
       </c>
@@ -9716,7 +9711,7 @@
         <v>24859.38177</v>
       </c>
     </row>
-    <row r="402" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A402" s="3">
         <v>45978</v>
       </c>
@@ -9739,7 +9734,7 @@
         <v>25311.7892599999</v>
       </c>
     </row>
-    <row r="403" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A403" s="3">
         <v>45978</v>
       </c>
@@ -9762,7 +9757,7 @@
         <v>25724.371078</v>
       </c>
     </row>
-    <row r="404" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A404" s="3">
         <v>45978</v>
       </c>
@@ -9785,7 +9780,7 @@
         <v>27020.841322</v>
       </c>
     </row>
-    <row r="405" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A405" s="3">
         <v>45978</v>
       </c>
@@ -9808,7 +9803,7 @@
         <v>26773.827746999999</v>
       </c>
     </row>
-    <row r="406" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A406" s="3">
         <v>45978</v>
       </c>
@@ -9831,7 +9826,7 @@
         <v>26064.900099999999</v>
       </c>
     </row>
-    <row r="407" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A407" s="3">
         <v>45978</v>
       </c>
@@ -9854,7 +9849,7 @@
         <v>25426.226901999999</v>
       </c>
     </row>
-    <row r="408" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A408" s="3">
         <v>45978</v>
       </c>
@@ -9877,7 +9872,7 @@
         <v>24727.682707</v>
       </c>
     </row>
-    <row r="409" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A409" s="3">
         <v>45978</v>
       </c>
@@ -9900,7 +9895,7 @@
         <v>23660.984830000001</v>
       </c>
     </row>
-    <row r="410" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A410" s="3">
         <v>45978</v>
       </c>
@@ -9923,7 +9918,7 @@
         <v>22532.530202999998</v>
       </c>
     </row>
-    <row r="411" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A411" s="3">
         <v>45979</v>
       </c>
@@ -9946,7 +9941,7 @@
         <v>21427.209102000001</v>
       </c>
     </row>
-    <row r="412" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A412" s="3">
         <v>45979</v>
       </c>
@@ -9969,7 +9964,7 @@
         <v>20537.061652</v>
       </c>
     </row>
-    <row r="413" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A413" s="3">
         <v>45979</v>
       </c>
@@ -9992,7 +9987,7 @@
         <v>20620.895270000001</v>
       </c>
     </row>
-    <row r="414" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A414" s="3">
         <v>45979</v>
       </c>
@@ -10015,7 +10010,7 @@
         <v>20361.243124000001</v>
       </c>
     </row>
-    <row r="415" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A415" s="3">
         <v>45979</v>
       </c>
@@ -10038,7 +10033,7 @@
         <v>20112.119568999999</v>
       </c>
     </row>
-    <row r="416" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A416" s="3">
         <v>45979</v>
       </c>
@@ -10061,7 +10056,7 @@
         <v>21284.045443999999</v>
       </c>
     </row>
-    <row r="417" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A417" s="3">
         <v>45979</v>
       </c>
@@ -10084,7 +10079,7 @@
         <v>23415.647592000001</v>
       </c>
     </row>
-    <row r="418" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A418" s="3">
         <v>45979</v>
       </c>
@@ -10107,7 +10102,7 @@
         <v>24117.205568000001</v>
       </c>
     </row>
-    <row r="419" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A419" s="3">
         <v>45979</v>
       </c>
@@ -10130,7 +10125,7 @@
         <v>24140.034094999999</v>
       </c>
     </row>
-    <row r="420" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A420" s="3">
         <v>45979</v>
       </c>
@@ -10153,7 +10148,7 @@
         <v>25707.474149000001</v>
       </c>
     </row>
-    <row r="421" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A421" s="3">
         <v>45979</v>
       </c>
@@ -10176,7 +10171,7 @@
         <v>26166.763768999899</v>
       </c>
     </row>
-    <row r="422" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A422" s="3">
         <v>45979</v>
       </c>
@@ -10199,7 +10194,7 @@
         <v>25785.278633999998</v>
       </c>
     </row>
-    <row r="423" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A423" s="3">
         <v>45979</v>
       </c>
@@ -10222,7 +10217,7 @@
         <v>24736.843024000002</v>
       </c>
     </row>
-    <row r="424" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A424" s="3">
         <v>45979</v>
       </c>
@@ -10245,7 +10240,7 @@
         <v>24737.511983999899</v>
       </c>
     </row>
-    <row r="425" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A425" s="3">
         <v>45979</v>
       </c>
@@ -10268,7 +10263,7 @@
         <v>24016.6038286</v>
       </c>
     </row>
-    <row r="426" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A426" s="3">
         <v>45979</v>
       </c>
@@ -10291,7 +10286,7 @@
         <v>23740.076835</v>
       </c>
     </row>
-    <row r="427" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A427" s="3">
         <v>45979</v>
       </c>
@@ -10314,7 +10309,7 @@
         <v>25027.041503</v>
       </c>
     </row>
-    <row r="428" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A428" s="3">
         <v>45979</v>
       </c>
@@ -10337,7 +10332,7 @@
         <v>26634.079526000001</v>
       </c>
     </row>
-    <row r="429" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A429" s="3">
         <v>45979</v>
       </c>
@@ -10360,7 +10355,7 @@
         <v>26585.661856999999</v>
       </c>
     </row>
-    <row r="430" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A430" s="3">
         <v>45979</v>
       </c>
@@ -10383,7 +10378,7 @@
         <v>26212.0745399999</v>
       </c>
     </row>
-    <row r="431" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A431" s="3">
         <v>45979</v>
       </c>
@@ -10406,7 +10401,7 @@
         <v>25762.237987</v>
       </c>
     </row>
-    <row r="432" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A432" s="3">
         <v>45979</v>
       </c>
@@ -10429,7 +10424,7 @@
         <v>25065.925691</v>
       </c>
     </row>
-    <row r="433" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A433" s="3">
         <v>45979</v>
       </c>
@@ -10452,7 +10447,7 @@
         <v>23785.798021999999</v>
       </c>
     </row>
-    <row r="434" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A434" s="3">
         <v>45979</v>
       </c>
@@ -10475,7 +10470,7 @@
         <v>22339.323511999999</v>
       </c>
     </row>
-    <row r="435" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A435" s="3">
         <v>45980</v>
       </c>
@@ -10498,7 +10493,7 @@
         <v>22047.732206000001</v>
       </c>
     </row>
-    <row r="436" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A436" s="3">
         <v>45980</v>
       </c>
@@ -10521,7 +10516,7 @@
         <v>21255.504394</v>
       </c>
     </row>
-    <row r="437" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A437" s="3">
         <v>45980</v>
       </c>
@@ -10544,7 +10539,7 @@
         <v>20811.850331000001</v>
       </c>
     </row>
-    <row r="438" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A438" s="3">
         <v>45980</v>
       </c>
@@ -10567,7 +10562,7 @@
         <v>20436.050014</v>
       </c>
     </row>
-    <row r="439" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A439" s="3">
         <v>45980</v>
       </c>
@@ -10590,7 +10585,7 @@
         <v>20519.839593000001</v>
       </c>
     </row>
-    <row r="440" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A440" s="3">
         <v>45980</v>
       </c>
@@ -10613,7 +10608,7 @@
         <v>21935.852815999999</v>
       </c>
     </row>
-    <row r="441" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A441" s="3">
         <v>45980</v>
       </c>
@@ -10636,7 +10631,7 @@
         <v>23897.990902000001</v>
       </c>
     </row>
-    <row r="442" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A442" s="3">
         <v>45980</v>
       </c>
@@ -10659,7 +10654,7 @@
         <v>24934.962203999999</v>
       </c>
     </row>
-    <row r="443" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A443" s="3">
         <v>45980</v>
       </c>
@@ -10682,7 +10677,7 @@
         <v>25913.439710999999</v>
       </c>
     </row>
-    <row r="444" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A444" s="3">
         <v>45980</v>
       </c>
@@ -10705,7 +10700,7 @@
         <v>25684.6491011</v>
       </c>
     </row>
-    <row r="445" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A445" s="3">
         <v>45980</v>
       </c>
@@ -10728,7 +10723,7 @@
         <v>26436.953259999998</v>
       </c>
     </row>
-    <row r="446" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A446" s="3">
         <v>45980</v>
       </c>
@@ -10751,7 +10746,7 @@
         <v>26448.661555999999</v>
       </c>
     </row>
-    <row r="447" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A447" s="3">
         <v>45980</v>
       </c>
@@ -10774,7 +10769,7 @@
         <v>26140.015477000001</v>
       </c>
     </row>
-    <row r="448" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A448" s="3">
         <v>45980</v>
       </c>
@@ -10797,7 +10792,7 @@
         <v>25740.743108999999</v>
       </c>
     </row>
-    <row r="449" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A449" s="3">
         <v>45980</v>
       </c>
@@ -10820,7 +10815,7 @@
         <v>25018.9581574</v>
       </c>
     </row>
-    <row r="450" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A450" s="3">
         <v>45980</v>
       </c>
@@ -10843,7 +10838,7 @@
         <v>24419.343207999998</v>
       </c>
     </row>
-    <row r="451" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A451" s="3">
         <v>45980</v>
       </c>
@@ -10866,7 +10861,7 @@
         <v>25711.150157</v>
       </c>
     </row>
-    <row r="452" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A452" s="3">
         <v>45980</v>
       </c>
@@ -10889,7 +10884,7 @@
         <v>26931.375102999998</v>
       </c>
     </row>
-    <row r="453" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A453" s="3">
         <v>45980</v>
       </c>
@@ -10912,7 +10907,7 @@
         <v>26751.013981</v>
       </c>
     </row>
-    <row r="454" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A454" s="3">
         <v>45980</v>
       </c>
@@ -10935,7 +10930,7 @@
         <v>26274.186807999999</v>
       </c>
     </row>
-    <row r="455" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A455" s="3">
         <v>45980</v>
       </c>
@@ -10958,7 +10953,7 @@
         <v>25757.029302999999</v>
       </c>
     </row>
-    <row r="456" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A456" s="3">
         <v>45980</v>
       </c>
@@ -10981,7 +10976,7 @@
         <v>25270.654537999999</v>
       </c>
     </row>
-    <row r="457" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A457" s="3">
         <v>45980</v>
       </c>
@@ -11004,7 +10999,7 @@
         <v>23941.551011</v>
       </c>
     </row>
-    <row r="458" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A458" s="3">
         <v>45980</v>
       </c>
@@ -11027,7 +11022,7 @@
         <v>22589.647658000002</v>
       </c>
     </row>
-    <row r="459" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A459" s="3">
         <v>45981</v>
       </c>
@@ -11050,7 +11045,7 @@
         <v>22138.103824999998</v>
       </c>
     </row>
-    <row r="460" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A460" s="3">
         <v>45981</v>
       </c>
@@ -11073,7 +11068,7 @@
         <v>21150.448413999999</v>
       </c>
     </row>
-    <row r="461" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A461" s="3">
         <v>45981</v>
       </c>
@@ -11096,7 +11091,7 @@
         <v>20979.825629999999</v>
       </c>
     </row>
-    <row r="462" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A462" s="3">
         <v>45981</v>
       </c>
@@ -11119,7 +11114,7 @@
         <v>20686.060724999999</v>
       </c>
     </row>
-    <row r="463" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A463" s="3">
         <v>45981</v>
       </c>
@@ -11142,7 +11137,7 @@
         <v>20739.049874999899</v>
       </c>
     </row>
-    <row r="464" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A464" s="3">
         <v>45981</v>
       </c>
@@ -11165,7 +11160,7 @@
         <v>21971.91589</v>
       </c>
     </row>
-    <row r="465" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A465" s="3">
         <v>45981</v>
       </c>
@@ -11188,7 +11183,7 @@
         <v>23740.189984000001</v>
       </c>
     </row>
-    <row r="466" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A466" s="3">
         <v>45981</v>
       </c>
@@ -11211,7 +11206,7 @@
         <v>25798.242234000001</v>
       </c>
     </row>
-    <row r="467" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A467" s="3">
         <v>45981</v>
       </c>
@@ -11234,7 +11229,7 @@
         <v>29034.522360999999</v>
       </c>
     </row>
-    <row r="468" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A468" s="3">
         <v>45981</v>
       </c>
@@ -11257,7 +11252,7 @@
         <v>29388.694415999998</v>
       </c>
     </row>
-    <row r="469" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A469" s="3">
         <v>45981</v>
       </c>
@@ -11280,7 +11275,7 @@
         <v>29333.836852</v>
       </c>
     </row>
-    <row r="470" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A470" s="3">
         <v>45981</v>
       </c>
@@ -11303,7 +11298,7 @@
         <v>29637.470923999899</v>
       </c>
     </row>
-    <row r="471" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A471" s="3">
         <v>45981</v>
       </c>
@@ -11326,7 +11321,7 @@
         <v>29084.664617999999</v>
       </c>
     </row>
-    <row r="472" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A472" s="3">
         <v>45981</v>
       </c>
@@ -11349,7 +11344,7 @@
         <v>28513.758517999999</v>
       </c>
     </row>
-    <row r="473" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A473" s="3">
         <v>45981</v>
       </c>
@@ -11372,7 +11367,7 @@
         <v>27050.098902999998</v>
       </c>
     </row>
-    <row r="474" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A474" s="3">
         <v>45981</v>
       </c>
@@ -11395,7 +11390,7 @@
         <v>25961.002484000001</v>
       </c>
     </row>
-    <row r="475" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A475" s="3">
         <v>45981</v>
       </c>
@@ -11418,7 +11413,7 @@
         <v>26281.459153</v>
       </c>
     </row>
-    <row r="476" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A476" s="3">
         <v>45981</v>
       </c>
@@ -11441,7 +11436,7 @@
         <v>27619.541963999902</v>
       </c>
     </row>
-    <row r="477" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A477" s="3">
         <v>45981</v>
       </c>
@@ -11464,7 +11459,7 @@
         <v>27169.77303</v>
       </c>
     </row>
-    <row r="478" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A478" s="3">
         <v>45981</v>
       </c>
@@ -11487,7 +11482,7 @@
         <v>26757.167452999998</v>
       </c>
     </row>
-    <row r="479" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A479" s="3">
         <v>45981</v>
       </c>
@@ -11510,7 +11505,7 @@
         <v>26355.420222000001</v>
       </c>
     </row>
-    <row r="480" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A480" s="3">
         <v>45981</v>
       </c>
@@ -11533,7 +11528,7 @@
         <v>25578.4866679999</v>
       </c>
     </row>
-    <row r="481" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A481" s="3">
         <v>45981</v>
       </c>
@@ -11556,7 +11551,7 @@
         <v>24316.313196999999</v>
       </c>
     </row>
-    <row r="482" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A482" s="3">
         <v>45981</v>
       </c>
@@ -11579,7 +11574,7 @@
         <v>23169.681524</v>
       </c>
     </row>
-    <row r="483" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A483" s="3">
         <v>45982</v>
       </c>
@@ -11602,7 +11597,7 @@
         <v>22500.37659</v>
       </c>
     </row>
-    <row r="484" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A484" s="3">
         <v>45982</v>
       </c>
@@ -11625,7 +11620,7 @@
         <v>21743.500034000001</v>
       </c>
     </row>
-    <row r="485" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A485" s="3">
         <v>45982</v>
       </c>
@@ -11648,7 +11643,7 @@
         <v>21755.769185000001</v>
       </c>
     </row>
-    <row r="486" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A486" s="3">
         <v>45982</v>
       </c>
@@ -11671,7 +11666,7 @@
         <v>21774.563051000001</v>
       </c>
     </row>
-    <row r="487" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A487" s="3">
         <v>45982</v>
       </c>
@@ -11694,7 +11689,7 @@
         <v>21366.667804000001</v>
       </c>
     </row>
-    <row r="488" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A488" s="3">
         <v>45982</v>
       </c>
@@ -11717,7 +11712,7 @@
         <v>22073.089605000001</v>
       </c>
     </row>
-    <row r="489" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A489" s="3">
         <v>45982</v>
       </c>
@@ -11740,7 +11735,7 @@
         <v>23883.886082000001</v>
       </c>
     </row>
-    <row r="490" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A490" s="3">
         <v>45982</v>
       </c>
@@ -11763,7 +11758,7 @@
         <v>24771.832929</v>
       </c>
     </row>
-    <row r="491" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A491" s="3">
         <v>45982</v>
       </c>
@@ -11786,7 +11781,7 @@
         <v>24870.220947000002</v>
       </c>
     </row>
-    <row r="492" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A492" s="3">
         <v>45982</v>
       </c>
@@ -11809,7 +11804,7 @@
         <v>23766.18723</v>
       </c>
     </row>
-    <row r="493" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A493" s="3">
         <v>45982</v>
       </c>
@@ -11832,7 +11827,7 @@
         <v>24004.399913000001</v>
       </c>
     </row>
-    <row r="494" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A494" s="3">
         <v>45982</v>
       </c>
@@ -11855,7 +11850,7 @@
         <v>23330.657153</v>
       </c>
     </row>
-    <row r="495" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A495" s="3">
         <v>45982</v>
       </c>
@@ -11878,7 +11873,7 @@
         <v>23456.623503999999</v>
       </c>
     </row>
-    <row r="496" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A496" s="3">
         <v>45982</v>
       </c>
@@ -11901,7 +11896,7 @@
         <v>24078.9868299999</v>
       </c>
     </row>
-    <row r="497" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A497" s="3">
         <v>45982</v>
       </c>
@@ -11924,7 +11919,7 @@
         <v>23407.255991999999</v>
       </c>
     </row>
-    <row r="498" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A498" s="3">
         <v>45982</v>
       </c>
@@ -11947,7 +11942,7 @@
         <v>23517.363647999999</v>
       </c>
     </row>
-    <row r="499" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A499" s="3">
         <v>45982</v>
       </c>
@@ -11970,7 +11965,7 @@
         <v>25379.988506999998</v>
       </c>
     </row>
-    <row r="500" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A500" s="3">
         <v>45982</v>
       </c>
@@ -11993,7 +11988,7 @@
         <v>26515.919006</v>
       </c>
     </row>
-    <row r="501" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A501" s="3">
         <v>45982</v>
       </c>
@@ -12016,7 +12011,7 @@
         <v>26272.099559999999</v>
       </c>
     </row>
-    <row r="502" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A502" s="3">
         <v>45982</v>
       </c>
@@ -12039,7 +12034,7 @@
         <v>25824.7005939999</v>
       </c>
     </row>
-    <row r="503" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A503" s="3">
         <v>45982</v>
       </c>
@@ -12062,7 +12057,7 @@
         <v>25298.449756999998</v>
       </c>
     </row>
-    <row r="504" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A504" s="3">
         <v>45982</v>
       </c>
@@ -12085,7 +12080,7 @@
         <v>24945.698779999999</v>
       </c>
     </row>
-    <row r="505" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A505" s="3">
         <v>45982</v>
       </c>
@@ -12108,7 +12103,7 @@
         <v>24117.169935999998</v>
       </c>
     </row>
-    <row r="506" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A506" s="3">
         <v>45982</v>
       </c>
@@ -12131,7 +12126,7 @@
         <v>23031.926716000002</v>
       </c>
     </row>
-    <row r="507" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A507" s="3">
         <v>45983</v>
       </c>
@@ -12154,7 +12149,7 @@
         <v>22196.413644</v>
       </c>
     </row>
-    <row r="508" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A508" s="3">
         <v>45983</v>
       </c>
@@ -12177,7 +12172,7 @@
         <v>21297.656211000001</v>
       </c>
     </row>
-    <row r="509" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A509" s="3">
         <v>45983</v>
       </c>
@@ -12200,7 +12195,7 @@
         <v>20553.133440000001</v>
       </c>
     </row>
-    <row r="510" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A510" s="3">
         <v>45983</v>
       </c>
@@ -12223,7 +12218,7 @@
         <v>20034.299267999999</v>
       </c>
     </row>
-    <row r="511" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A511" s="3">
         <v>45983</v>
       </c>
@@ -12246,7 +12241,7 @@
         <v>20121.762834000001</v>
       </c>
     </row>
-    <row r="512" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A512" s="3">
         <v>45983</v>
       </c>
@@ -12269,7 +12264,7 @@
         <v>20505.904323999999</v>
       </c>
     </row>
-    <row r="513" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A513" s="3">
         <v>45983</v>
       </c>
@@ -12292,7 +12287,7 @@
         <v>21394.558322000001</v>
       </c>
     </row>
-    <row r="514" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A514" s="3">
         <v>45983</v>
       </c>
@@ -12315,7 +12310,7 @@
         <v>21827.738776999999</v>
       </c>
     </row>
-    <row r="515" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A515" s="3">
         <v>45983</v>
       </c>
@@ -12338,7 +12333,7 @@
         <v>21941.571497000001</v>
       </c>
     </row>
-    <row r="516" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A516" s="3">
         <v>45983</v>
       </c>
@@ -12361,7 +12356,7 @@
         <v>21504.596567999899</v>
       </c>
     </row>
-    <row r="517" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A517" s="3">
         <v>45983</v>
       </c>
@@ -12384,7 +12379,7 @@
         <v>22669.171684000001</v>
       </c>
     </row>
-    <row r="518" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A518" s="3">
         <v>45983</v>
       </c>
@@ -12407,7 +12402,7 @@
         <v>22946.678564999998</v>
       </c>
     </row>
-    <row r="519" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A519" s="3">
         <v>45983</v>
       </c>
@@ -12430,7 +12425,7 @@
         <v>23566.060965000001</v>
       </c>
     </row>
-    <row r="520" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A520" s="3">
         <v>45983</v>
       </c>
@@ -12453,7 +12448,7 @@
         <v>23575.831324999999</v>
       </c>
     </row>
-    <row r="521" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A521" s="3">
         <v>45983</v>
       </c>
@@ -12476,7 +12471,7 @@
         <v>22901.0691569999</v>
       </c>
     </row>
-    <row r="522" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A522" s="3">
         <v>45983</v>
       </c>
@@ -12499,7 +12494,7 @@
         <v>22475.927833999998</v>
       </c>
     </row>
-    <row r="523" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A523" s="3">
         <v>45983</v>
       </c>
@@ -12522,7 +12517,7 @@
         <v>23630.950848</v>
       </c>
     </row>
-    <row r="524" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A524" s="3">
         <v>45983</v>
       </c>
@@ -12545,7 +12540,7 @@
         <v>24815.140685999999</v>
       </c>
     </row>
-    <row r="525" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A525" s="3">
         <v>45983</v>
       </c>
@@ -12568,7 +12563,7 @@
         <v>24550.116177</v>
       </c>
     </row>
-    <row r="526" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A526" s="3">
         <v>45983</v>
       </c>
@@ -12591,7 +12586,7 @@
         <v>24286.389436000001</v>
       </c>
     </row>
-    <row r="527" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A527" s="3">
         <v>45983</v>
       </c>
@@ -12614,7 +12609,7 @@
         <v>23749.876934</v>
       </c>
     </row>
-    <row r="528" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A528" s="3">
         <v>45983</v>
       </c>
@@ -12637,7 +12632,7 @@
         <v>23625.511454</v>
       </c>
     </row>
-    <row r="529" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A529" s="3">
         <v>45983</v>
       </c>
@@ -12660,7 +12655,7 @@
         <v>22782.645594000001</v>
       </c>
     </row>
-    <row r="530" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A530" s="3">
         <v>45983</v>
       </c>
@@ -12683,7 +12678,7 @@
         <v>21857.998448999999</v>
       </c>
     </row>
-    <row r="531" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A531" s="3">
         <v>45984</v>
       </c>
@@ -12706,7 +12701,7 @@
         <v>21386.406885999899</v>
       </c>
     </row>
-    <row r="532" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A532" s="3">
         <v>45984</v>
       </c>
@@ -12729,7 +12724,7 @@
         <v>20379.368503999998</v>
       </c>
     </row>
-    <row r="533" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A533" s="3">
         <v>45984</v>
       </c>
@@ -12752,7 +12747,7 @@
         <v>19618.223456</v>
       </c>
     </row>
-    <row r="534" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A534" s="3">
         <v>45984</v>
       </c>
@@ -12775,7 +12770,7 @@
         <v>19285.924349000001</v>
       </c>
     </row>
-    <row r="535" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A535" s="3">
         <v>45984</v>
       </c>
@@ -12798,7 +12793,7 @@
         <v>19182.315055999999</v>
       </c>
     </row>
-    <row r="536" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A536" s="3">
         <v>45984</v>
       </c>
@@ -12821,7 +12816,7 @@
         <v>19659.465069999998</v>
       </c>
     </row>
-    <row r="537" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A537" s="3">
         <v>45984</v>
       </c>
@@ -12844,7 +12839,7 @@
         <v>20194.838468999998</v>
       </c>
     </row>
-    <row r="538" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A538" s="3">
         <v>45984</v>
       </c>
@@ -12867,7 +12862,7 @@
         <v>20523.342358000002</v>
       </c>
     </row>
-    <row r="539" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A539" s="3">
         <v>45984</v>
       </c>
@@ -12890,7 +12885,7 @@
         <v>21197.709654390001</v>
       </c>
     </row>
-    <row r="540" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A540" s="3">
         <v>45984</v>
       </c>
@@ -12913,7 +12908,7 @@
         <v>21946.6526466</v>
       </c>
     </row>
-    <row r="541" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A541" s="3">
         <v>45984</v>
       </c>
@@ -12936,7 +12931,7 @@
         <v>21849.160269100001</v>
       </c>
     </row>
-    <row r="542" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A542" s="3">
         <v>45984</v>
       </c>
@@ -12959,7 +12954,7 @@
         <v>22448.988131299899</v>
       </c>
     </row>
-    <row r="543" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A543" s="3">
         <v>45984</v>
       </c>
@@ -12982,7 +12977,7 @@
         <v>21943.90564746</v>
       </c>
     </row>
-    <row r="544" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A544" s="3">
         <v>45984</v>
       </c>
@@ -13005,7 +13000,7 @@
         <v>23214.468282599999</v>
       </c>
     </row>
-    <row r="545" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A545" s="3">
         <v>45984</v>
       </c>
@@ -13028,7 +13023,7 @@
         <v>22885.1014379999</v>
       </c>
     </row>
-    <row r="546" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A546" s="3">
         <v>45984</v>
       </c>
@@ -13051,7 +13046,7 @@
         <v>21453.187984</v>
       </c>
     </row>
-    <row r="547" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A547" s="3">
         <v>45984</v>
       </c>
@@ -13074,7 +13069,7 @@
         <v>23062.865861999999</v>
       </c>
     </row>
-    <row r="548" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A548" s="3">
         <v>45984</v>
       </c>
@@ -13097,7 +13092,7 @@
         <v>24878.473744999999</v>
       </c>
     </row>
-    <row r="549" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A549" s="3">
         <v>45984</v>
       </c>
@@ -13120,7 +13115,7 @@
         <v>24765.260865</v>
       </c>
     </row>
-    <row r="550" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A550" s="3">
         <v>45984</v>
       </c>
@@ -13143,7 +13138,7 @@
         <v>24255.627961999999</v>
       </c>
     </row>
-    <row r="551" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A551" s="3">
         <v>45984</v>
       </c>
@@ -13166,7 +13161,7 @@
         <v>23677.602025</v>
       </c>
     </row>
-    <row r="552" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A552" s="3">
         <v>45984</v>
       </c>
@@ -13189,7 +13184,7 @@
         <v>23337.432505999899</v>
       </c>
     </row>
-    <row r="553" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A553" s="3">
         <v>45984</v>
       </c>
@@ -13212,7 +13207,7 @@
         <v>22663.80185</v>
       </c>
     </row>
-    <row r="554" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A554" s="3">
         <v>45984</v>
       </c>
@@ -13235,7 +13230,7 @@
         <v>21611.140687999999</v>
       </c>
     </row>
-    <row r="555" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A555" s="3">
         <v>45985</v>
       </c>
@@ -13258,7 +13253,7 @@
         <v>21160.139101000001</v>
       </c>
     </row>
-    <row r="556" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A556" s="3">
         <v>45985</v>
       </c>
@@ -13281,7 +13276,7 @@
         <v>20599.819811000001</v>
       </c>
     </row>
-    <row r="557" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A557" s="3">
         <v>45985</v>
       </c>
@@ -13304,7 +13299,7 @@
         <v>20973.771518000001</v>
       </c>
     </row>
-    <row r="558" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A558" s="3">
         <v>45985</v>
       </c>
@@ -13327,7 +13322,7 @@
         <v>20259.937182999998</v>
       </c>
     </row>
-    <row r="559" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A559" s="3">
         <v>45985</v>
       </c>
@@ -13350,7 +13345,7 @@
         <v>20873.113867</v>
       </c>
     </row>
-    <row r="560" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A560" s="3">
         <v>45985</v>
       </c>
@@ -13373,7 +13368,7 @@
         <v>21848.551040999999</v>
       </c>
     </row>
-    <row r="561" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A561" s="3">
         <v>45985</v>
       </c>
@@ -13396,7 +13391,7 @@
         <v>23204.900538999998</v>
       </c>
     </row>
-    <row r="562" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A562" s="3">
         <v>45985</v>
       </c>
@@ -13419,7 +13414,7 @@
         <v>24544.562341999899</v>
       </c>
     </row>
-    <row r="563" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A563" s="3">
         <v>45985</v>
       </c>
@@ -13442,7 +13437,7 @@
         <v>26678.088432</v>
       </c>
     </row>
-    <row r="564" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A564" s="3">
         <v>45985</v>
       </c>
@@ -13465,7 +13460,7 @@
         <v>26211.271671999999</v>
       </c>
     </row>
-    <row r="565" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A565" s="3">
         <v>45985</v>
       </c>
@@ -13488,7 +13483,7 @@
         <v>26207.049306000001</v>
       </c>
     </row>
-    <row r="566" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A566" s="3">
         <v>45985</v>
       </c>
@@ -13511,7 +13506,7 @@
         <v>26032.183270000001</v>
       </c>
     </row>
-    <row r="567" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A567" s="3">
         <v>45985</v>
       </c>
@@ -13534,7 +13529,7 @@
         <v>26083.409524999999</v>
       </c>
     </row>
-    <row r="568" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A568" s="3">
         <v>45985</v>
       </c>
@@ -13557,7 +13552,7 @@
         <v>27119.040773000001</v>
       </c>
     </row>
-    <row r="569" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A569" s="3">
         <v>45985</v>
       </c>
@@ -13580,7 +13575,7 @@
         <v>26744.974678999999</v>
       </c>
     </row>
-    <row r="570" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A570" s="3">
         <v>45985</v>
       </c>
@@ -13603,7 +13598,7 @@
         <v>24783.787346999899</v>
       </c>
     </row>
-    <row r="571" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A571" s="3">
         <v>45985</v>
       </c>
@@ -13626,7 +13621,7 @@
         <v>25633.356179999999</v>
       </c>
     </row>
-    <row r="572" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A572" s="3">
         <v>45985</v>
       </c>
@@ -13649,7 +13644,7 @@
         <v>26862.813241</v>
       </c>
     </row>
-    <row r="573" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A573" s="3">
         <v>45985</v>
       </c>
@@ -13672,7 +13667,7 @@
         <v>26423.631685</v>
       </c>
     </row>
-    <row r="574" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A574" s="3">
         <v>45985</v>
       </c>
@@ -13695,7 +13690,7 @@
         <v>25985.028885</v>
       </c>
     </row>
-    <row r="575" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A575" s="3">
         <v>45985</v>
       </c>
@@ -13718,7 +13713,7 @@
         <v>25346.688651</v>
       </c>
     </row>
-    <row r="576" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A576" s="3">
         <v>45985</v>
       </c>
@@ -13741,7 +13736,7 @@
         <v>25123.080223000001</v>
       </c>
     </row>
-    <row r="577" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A577" s="3">
         <v>45985</v>
       </c>
@@ -13764,7 +13759,7 @@
         <v>24065.262069</v>
       </c>
     </row>
-    <row r="578" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A578" s="3">
         <v>45985</v>
       </c>
@@ -13787,7 +13782,7 @@
         <v>22730.525914999998</v>
       </c>
     </row>
-    <row r="579" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A579" s="3">
         <v>45986</v>
       </c>
@@ -13810,7 +13805,7 @@
         <v>22110.022638999999</v>
       </c>
     </row>
-    <row r="580" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A580" s="3">
         <v>45986</v>
       </c>
@@ -13833,7 +13828,7 @@
         <v>21350.636427000001</v>
       </c>
     </row>
-    <row r="581" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A581" s="3">
         <v>45986</v>
       </c>
@@ -13856,7 +13851,7 @@
         <v>21325.286099999899</v>
       </c>
     </row>
-    <row r="582" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A582" s="3">
         <v>45986</v>
       </c>
@@ -13879,7 +13874,7 @@
         <v>20948.521558</v>
       </c>
     </row>
-    <row r="583" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A583" s="3">
         <v>45986</v>
       </c>
@@ -13902,7 +13897,7 @@
         <v>20968.484830000001</v>
       </c>
     </row>
-    <row r="584" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A584" s="3">
         <v>45986</v>
       </c>
@@ -13925,7 +13920,7 @@
         <v>22239.075054000001</v>
       </c>
     </row>
-    <row r="585" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A585" s="3">
         <v>45986</v>
       </c>
@@ -13948,7 +13943,7 @@
         <v>23791.616404</v>
       </c>
     </row>
-    <row r="586" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A586" s="3">
         <v>45986</v>
       </c>
@@ -13971,7 +13966,7 @@
         <v>24759.204544</v>
       </c>
     </row>
-    <row r="587" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A587" s="3">
         <v>45986</v>
       </c>
@@ -13994,7 +13989,7 @@
         <v>26289.094787999999</v>
       </c>
     </row>
-    <row r="588" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A588" s="3">
         <v>45986</v>
       </c>
@@ -14017,7 +14012,7 @@
         <v>27079.567824999998</v>
       </c>
     </row>
-    <row r="589" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A589" s="3">
         <v>45986</v>
       </c>
@@ -14040,7 +14035,7 @@
         <v>27181.1784989999</v>
       </c>
     </row>
-    <row r="590" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A590" s="3">
         <v>45986</v>
       </c>
@@ -14063,7 +14058,7 @@
         <v>27006.086173</v>
       </c>
     </row>
-    <row r="591" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A591" s="3">
         <v>45986</v>
       </c>
@@ -14086,7 +14081,7 @@
         <v>26808.804689000001</v>
       </c>
     </row>
-    <row r="592" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A592" s="3">
         <v>45986</v>
       </c>
@@ -14109,7 +14104,7 @@
         <v>27479.968815</v>
       </c>
     </row>
-    <row r="593" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A593" s="3">
         <v>45986</v>
       </c>
@@ -14132,7 +14127,7 @@
         <v>27224.997020999999</v>
       </c>
     </row>
-    <row r="594" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A594" s="3">
         <v>45986</v>
       </c>
@@ -14155,7 +14150,7 @@
         <v>25438.315144</v>
       </c>
     </row>
-    <row r="595" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A595" s="3">
         <v>45986</v>
       </c>
@@ -14178,7 +14173,7 @@
         <v>26148.071137999999</v>
       </c>
     </row>
-    <row r="596" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A596" s="3">
         <v>45986</v>
       </c>
@@ -14201,7 +14196,7 @@
         <v>27190.024389999999</v>
       </c>
     </row>
-    <row r="597" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A597" s="3">
         <v>45986</v>
       </c>
@@ -14224,7 +14219,7 @@
         <v>26930.000842000001</v>
       </c>
     </row>
-    <row r="598" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A598" s="3">
         <v>45986</v>
       </c>
@@ -14247,7 +14242,7 @@
         <v>26406.632320000001</v>
       </c>
     </row>
-    <row r="599" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A599" s="3">
         <v>45986</v>
       </c>
@@ -14270,7 +14265,7 @@
         <v>25862.956096999998</v>
       </c>
     </row>
-    <row r="600" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A600" s="3">
         <v>45986</v>
       </c>
@@ -14293,7 +14288,7 @@
         <v>25465.120525999999</v>
       </c>
     </row>
-    <row r="601" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A601" s="3">
         <v>45986</v>
       </c>
@@ -14316,7 +14311,7 @@
         <v>24387.172616</v>
       </c>
     </row>
-    <row r="602" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A602" s="3">
         <v>45986</v>
       </c>
@@ -14339,7 +14334,7 @@
         <v>23545.460020999999</v>
       </c>
     </row>
-    <row r="603" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A603" s="3">
         <v>45987</v>
       </c>
@@ -14362,7 +14357,7 @@
         <v>22869.125043</v>
       </c>
     </row>
-    <row r="604" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A604" s="3">
         <v>45987</v>
       </c>
@@ -14385,7 +14380,7 @@
         <v>22071.782842000001</v>
       </c>
     </row>
-    <row r="605" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A605" s="3">
         <v>45987</v>
       </c>
@@ -14408,7 +14403,7 @@
         <v>21594.211360000001</v>
       </c>
     </row>
-    <row r="606" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A606" s="3">
         <v>45987</v>
       </c>
@@ -14431,7 +14426,7 @@
         <v>21119.748152</v>
       </c>
     </row>
-    <row r="607" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A607" s="3">
         <v>45987</v>
       </c>
@@ -14454,7 +14449,7 @@
         <v>21529.496384999999</v>
       </c>
     </row>
-    <row r="608" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A608" s="3">
         <v>45987</v>
       </c>
@@ -14477,7 +14472,7 @@
         <v>22723.179282000001</v>
       </c>
     </row>
-    <row r="609" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A609" s="3">
         <v>45987</v>
       </c>
@@ -14500,7 +14495,7 @@
         <v>23861.907558999999</v>
       </c>
     </row>
-    <row r="610" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A610" s="3">
         <v>45987</v>
       </c>
@@ -14523,7 +14518,7 @@
         <v>24815.021092999999</v>
       </c>
     </row>
-    <row r="611" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A611" s="3">
         <v>45987</v>
       </c>
@@ -14546,7 +14541,7 @@
         <v>27256.7918069999</v>
       </c>
     </row>
-    <row r="612" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A612" s="3">
         <v>45987</v>
       </c>
@@ -14569,7 +14564,7 @@
         <v>28037.101431999999</v>
       </c>
     </row>
-    <row r="613" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A613" s="3">
         <v>45987</v>
       </c>
@@ -14592,7 +14587,7 @@
         <v>28069.67265</v>
       </c>
     </row>
-    <row r="614" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A614" s="3">
         <v>45987</v>
       </c>
@@ -14615,7 +14610,7 @@
         <v>27910.640189999998</v>
       </c>
     </row>
-    <row r="615" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A615" s="3">
         <v>45987</v>
       </c>
@@ -14638,7 +14633,7 @@
         <v>28116.320555999999</v>
       </c>
     </row>
-    <row r="616" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A616" s="3">
         <v>45987</v>
       </c>
@@ -14661,7 +14656,7 @@
         <v>27839.338173999899</v>
       </c>
     </row>
-    <row r="617" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A617" s="3">
         <v>45987</v>
       </c>
@@ -14684,7 +14679,7 @@
         <v>26849.549846999998</v>
       </c>
     </row>
-    <row r="618" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A618" s="3">
         <v>45987</v>
       </c>
@@ -14707,7 +14702,7 @@
         <v>25217.6130869999</v>
       </c>
     </row>
-    <row r="619" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A619" s="3">
         <v>45987</v>
       </c>
@@ -14730,7 +14725,7 @@
         <v>26263.51023</v>
       </c>
     </row>
-    <row r="620" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A620" s="3">
         <v>45987</v>
       </c>
@@ -14753,7 +14748,7 @@
         <v>27164.345106000001</v>
       </c>
     </row>
-    <row r="621" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A621" s="3">
         <v>45987</v>
       </c>
@@ -14776,7 +14771,7 @@
         <v>26719.3533399999</v>
       </c>
     </row>
-    <row r="622" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A622" s="3">
         <v>45987</v>
       </c>
@@ -14799,7 +14794,7 @@
         <v>26093.790486999998</v>
       </c>
     </row>
-    <row r="623" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A623" s="3">
         <v>45987</v>
       </c>
@@ -14822,7 +14817,7 @@
         <v>25553.38133</v>
       </c>
     </row>
-    <row r="624" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A624" s="3">
         <v>45987</v>
       </c>
@@ -14845,7 +14840,7 @@
         <v>25290.307568999899</v>
       </c>
     </row>
-    <row r="625" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A625" s="3">
         <v>45987</v>
       </c>
@@ -14868,7 +14863,7 @@
         <v>24536.498989</v>
       </c>
     </row>
-    <row r="626" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A626" s="3">
         <v>45987</v>
       </c>
@@ -14891,7 +14886,7 @@
         <v>23002.032093000002</v>
       </c>
     </row>
-    <row r="627" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A627" s="3">
         <v>45988</v>
       </c>
@@ -14914,7 +14909,7 @@
         <v>22478.879549000001</v>
       </c>
     </row>
-    <row r="628" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A628" s="3">
         <v>45988</v>
       </c>
@@ -14937,7 +14932,7 @@
         <v>21383.625335999899</v>
       </c>
     </row>
-    <row r="629" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A629" s="3">
         <v>45988</v>
       </c>
@@ -14960,7 +14955,7 @@
         <v>20505.979201999999</v>
       </c>
     </row>
-    <row r="630" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A630" s="3">
         <v>45988</v>
       </c>
@@ -14983,7 +14978,7 @@
         <v>20179.758934000001</v>
       </c>
     </row>
-    <row r="631" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A631" s="3">
         <v>45988</v>
       </c>
@@ -15006,7 +15001,7 @@
         <v>20118.74987</v>
       </c>
     </row>
-    <row r="632" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A632" s="3">
         <v>45988</v>
       </c>
@@ -15029,7 +15024,7 @@
         <v>20568.756365000001</v>
       </c>
     </row>
-    <row r="633" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A633" s="3">
         <v>45988</v>
       </c>
@@ -15052,7 +15047,7 @@
         <v>21305.316468999899</v>
       </c>
     </row>
-    <row r="634" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A634" s="3">
         <v>45988</v>
       </c>
@@ -15075,7 +15070,7 @@
         <v>22150.374566999999</v>
       </c>
     </row>
-    <row r="635" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A635" s="3">
         <v>45988</v>
       </c>
@@ -15098,7 +15093,7 @@
         <v>24833.192512000001</v>
       </c>
     </row>
-    <row r="636" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A636" s="3">
         <v>45988</v>
       </c>
@@ -15121,7 +15116,7 @@
         <v>25672.292605999999</v>
       </c>
     </row>
-    <row r="637" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A637" s="3">
         <v>45988</v>
       </c>
@@ -15144,7 +15139,7 @@
         <v>26978.433423999999</v>
       </c>
     </row>
-    <row r="638" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A638" s="3">
         <v>45988</v>
       </c>
@@ -15167,7 +15162,7 @@
         <v>26939.092307999999</v>
       </c>
     </row>
-    <row r="639" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A639" s="3">
         <v>45988</v>
       </c>
@@ -15190,7 +15185,7 @@
         <v>25921.902019000001</v>
       </c>
     </row>
-    <row r="640" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A640" s="3">
         <v>45988</v>
       </c>
@@ -15213,7 +15208,7 @@
         <v>25351.258271999999</v>
       </c>
     </row>
-    <row r="641" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A641" s="3">
         <v>45988</v>
       </c>
@@ -15236,7 +15231,7 @@
         <v>24491.790593000002</v>
       </c>
     </row>
-    <row r="642" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A642" s="3">
         <v>45988</v>
       </c>
@@ -15259,7 +15254,7 @@
         <v>23426.192867999998</v>
       </c>
     </row>
-    <row r="643" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A643" s="3">
         <v>45988</v>
       </c>
@@ -15282,7 +15277,7 @@
         <v>23930.150815000001</v>
       </c>
     </row>
-    <row r="644" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A644" s="3">
         <v>45988</v>
       </c>
@@ -15305,7 +15300,7 @@
         <v>23974.785723000001</v>
       </c>
     </row>
-    <row r="645" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A645" s="3">
         <v>45988</v>
       </c>
@@ -15328,7 +15323,7 @@
         <v>23167.860354</v>
       </c>
     </row>
-    <row r="646" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A646" s="3">
         <v>45988</v>
       </c>
@@ -15351,7 +15346,7 @@
         <v>22593.3265709999</v>
       </c>
     </row>
-    <row r="647" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A647" s="3">
         <v>45988</v>
       </c>
@@ -15374,7 +15369,7 @@
         <v>22435.801135000002</v>
       </c>
     </row>
-    <row r="648" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A648" s="3">
         <v>45988</v>
       </c>
@@ -15397,7 +15392,7 @@
         <v>22526.269833999999</v>
       </c>
     </row>
-    <row r="649" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A649" s="3">
         <v>45988</v>
       </c>
@@ -15420,7 +15415,7 @@
         <v>21951.4148189999</v>
       </c>
     </row>
-    <row r="650" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A650" s="3">
         <v>45988</v>
       </c>
@@ -15443,7 +15438,7 @@
         <v>21123.683125</v>
       </c>
     </row>
-    <row r="651" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A651" s="3">
         <v>45989</v>
       </c>
@@ -15466,7 +15461,7 @@
         <v>20913.218061</v>
       </c>
     </row>
-    <row r="652" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A652" s="3">
         <v>45989</v>
       </c>
@@ -15489,7 +15484,7 @@
         <v>20245.484367000001</v>
       </c>
     </row>
-    <row r="653" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A653" s="3">
         <v>45989</v>
       </c>
@@ -15512,7 +15507,7 @@
         <v>19724.376970000001</v>
       </c>
     </row>
-    <row r="654" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A654" s="3">
         <v>45989</v>
       </c>
@@ -15535,7 +15530,7 @@
         <v>19439.902581999999</v>
       </c>
     </row>
-    <row r="655" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A655" s="3">
         <v>45989</v>
       </c>
@@ -15558,7 +15553,7 @@
         <v>19633.5336289999</v>
       </c>
     </row>
-    <row r="656" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A656" s="3">
         <v>45989</v>
       </c>
@@ -15581,7 +15576,7 @@
         <v>20478.231943999999</v>
       </c>
     </row>
-    <row r="657" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A657" s="3">
         <v>45989</v>
       </c>
@@ -15604,7 +15599,7 @@
         <v>21692.883533</v>
       </c>
     </row>
-    <row r="658" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A658" s="3">
         <v>45989</v>
       </c>
@@ -15627,7 +15622,7 @@
         <v>22528.582577000001</v>
       </c>
     </row>
-    <row r="659" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A659" s="3">
         <v>45989</v>
       </c>
@@ -15650,7 +15645,7 @@
         <v>24867.763014</v>
       </c>
     </row>
-    <row r="660" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A660" s="3">
         <v>45989</v>
       </c>
@@ -15673,7 +15668,7 @@
         <v>25871.290464999998</v>
       </c>
     </row>
-    <row r="661" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A661" s="3">
         <v>45989</v>
       </c>
@@ -15696,7 +15691,7 @@
         <v>26449.891177000001</v>
       </c>
     </row>
-    <row r="662" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A662" s="3">
         <v>45989</v>
       </c>
@@ -15719,7 +15714,7 @@
         <v>26249.8049609999</v>
       </c>
     </row>
-    <row r="663" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A663" s="3">
         <v>45989</v>
       </c>
@@ -15742,7 +15737,7 @@
         <v>26306.782636</v>
       </c>
     </row>
-    <row r="664" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A664" s="3">
         <v>45989</v>
       </c>
@@ -15765,7 +15760,7 @@
         <v>26599.202232</v>
       </c>
     </row>
-    <row r="665" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A665" s="3">
         <v>45989</v>
       </c>
@@ -15788,7 +15783,7 @@
         <v>25201.651779</v>
       </c>
     </row>
-    <row r="666" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A666" s="3">
         <v>45989</v>
       </c>
@@ -15811,7 +15806,7 @@
         <v>23913.207933999998</v>
       </c>
     </row>
-    <row r="667" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A667" s="3">
         <v>45989</v>
       </c>
@@ -15834,7 +15829,7 @@
         <v>24860.266517</v>
       </c>
     </row>
-    <row r="668" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A668" s="3">
         <v>45989</v>
       </c>
@@ -15857,7 +15852,7 @@
         <v>26129.9768469999</v>
       </c>
     </row>
-    <row r="669" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A669" s="3">
         <v>45989</v>
       </c>
@@ -15880,7 +15875,7 @@
         <v>25578.691695000001</v>
       </c>
     </row>
-    <row r="670" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A670" s="3">
         <v>45989</v>
       </c>
@@ -15903,7 +15898,7 @@
         <v>25235.606427999999</v>
       </c>
     </row>
-    <row r="671" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A671" s="3">
         <v>45989</v>
       </c>
@@ -15926,7 +15921,7 @@
         <v>24692.759886</v>
       </c>
     </row>
-    <row r="672" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A672" s="3">
         <v>45989</v>
       </c>
@@ -15949,7 +15944,7 @@
         <v>24357.795880000001</v>
       </c>
     </row>
-    <row r="673" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A673" s="3">
         <v>45989</v>
       </c>
@@ -15972,7 +15967,7 @@
         <v>23461.259331000001</v>
       </c>
     </row>
-    <row r="674" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A674" s="3">
         <v>45989</v>
       </c>
@@ -15995,7 +15990,7 @@
         <v>22319.4169039999</v>
       </c>
     </row>
-    <row r="675" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A675" s="3">
         <v>45990</v>
       </c>
@@ -16018,7 +16013,7 @@
         <v>21711.3507509999</v>
       </c>
     </row>
-    <row r="676" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A676" s="3">
         <v>45990</v>
       </c>
@@ -16041,7 +16036,7 @@
         <v>20629.646250999998</v>
       </c>
     </row>
-    <row r="677" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A677" s="3">
         <v>45990</v>
       </c>
@@ -16064,7 +16059,7 @@
         <v>19851.647186999999</v>
       </c>
     </row>
-    <row r="678" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A678" s="3">
         <v>45990</v>
       </c>
@@ -16087,7 +16082,7 @@
         <v>19564.150860999998</v>
       </c>
     </row>
-    <row r="679" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A679" s="3">
         <v>45990</v>
       </c>
@@ -16110,7 +16105,7 @@
         <v>19615.099317</v>
       </c>
     </row>
-    <row r="680" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A680" s="3">
         <v>45990</v>
       </c>
@@ -16133,7 +16128,7 @@
         <v>20180.950068999999</v>
       </c>
     </row>
-    <row r="681" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A681" s="3">
         <v>45990</v>
       </c>
@@ -16156,7 +16151,7 @@
         <v>20969.642402000001</v>
       </c>
     </row>
-    <row r="682" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A682" s="3">
         <v>45990</v>
       </c>
@@ -16179,7 +16174,7 @@
         <v>21872.2357229999</v>
       </c>
     </row>
-    <row r="683" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A683" s="3">
         <v>45990</v>
       </c>
@@ -16202,7 +16197,7 @@
         <v>23958.708861999999</v>
       </c>
     </row>
-    <row r="684" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A684" s="3">
         <v>45990</v>
       </c>
@@ -16225,7 +16220,7 @@
         <v>25409.517115999999</v>
       </c>
     </row>
-    <row r="685" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A685" s="3">
         <v>45990</v>
       </c>
@@ -16248,7 +16243,7 @@
         <v>26124.7746989999</v>
       </c>
     </row>
-    <row r="686" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A686" s="3">
         <v>45990</v>
       </c>
@@ -16271,7 +16266,7 @@
         <v>25564.625796</v>
       </c>
     </row>
-    <row r="687" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A687" s="3">
         <v>45990</v>
       </c>
@@ -16294,7 +16289,7 @@
         <v>25561.4256189999</v>
       </c>
     </row>
-    <row r="688" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A688" s="3">
         <v>45990</v>
       </c>
@@ -16317,7 +16312,7 @@
         <v>25891.904700999999</v>
       </c>
     </row>
-    <row r="689" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A689" s="3">
         <v>45990</v>
       </c>
@@ -16340,7 +16335,7 @@
         <v>25310.531652999998</v>
       </c>
     </row>
-    <row r="690" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A690" s="3">
         <v>45990</v>
       </c>
@@ -16363,7 +16358,7 @@
         <v>22943.399974</v>
       </c>
     </row>
-    <row r="691" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A691" s="3">
         <v>45990</v>
       </c>
@@ -16386,7 +16381,7 @@
         <v>24235.139386999999</v>
       </c>
     </row>
-    <row r="692" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A692" s="3">
         <v>45990</v>
       </c>
@@ -16409,7 +16404,7 @@
         <v>25403.267855999999</v>
       </c>
     </row>
-    <row r="693" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A693" s="3">
         <v>45990</v>
       </c>
@@ -16432,7 +16427,7 @@
         <v>25258.5389269999</v>
       </c>
     </row>
-    <row r="694" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A694" s="3">
         <v>45990</v>
       </c>
@@ -16455,7 +16450,7 @@
         <v>24812.278384000001</v>
       </c>
     </row>
-    <row r="695" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A695" s="3">
         <v>45990</v>
       </c>
@@ -16478,7 +16473,7 @@
         <v>24317.916738</v>
       </c>
     </row>
-    <row r="696" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A696" s="3">
         <v>45990</v>
       </c>
@@ -16501,7 +16496,7 @@
         <v>24078.268765000001</v>
       </c>
     </row>
-    <row r="697" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A697" s="3">
         <v>45990</v>
       </c>
@@ -16524,7 +16519,7 @@
         <v>23204.309515000001</v>
       </c>
     </row>
-    <row r="698" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A698" s="3">
         <v>45990</v>
       </c>
@@ -16547,7 +16542,7 @@
         <v>22036.440719999999</v>
       </c>
     </row>
-    <row r="699" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A699" s="3">
         <v>45991</v>
       </c>
@@ -16570,7 +16565,7 @@
         <v>21574.355382000002</v>
       </c>
     </row>
-    <row r="700" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A700" s="3">
         <v>45991</v>
       </c>
@@ -16593,7 +16588,7 @@
         <v>20718.129293999998</v>
       </c>
     </row>
-    <row r="701" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A701" s="3">
         <v>45991</v>
       </c>
@@ -16616,7 +16611,7 @@
         <v>20144.462983000001</v>
       </c>
     </row>
-    <row r="702" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A702" s="3">
         <v>45991</v>
       </c>
@@ -16639,7 +16634,7 @@
         <v>19726.027833</v>
       </c>
     </row>
-    <row r="703" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A703" s="3">
         <v>45991</v>
       </c>
@@ -16662,7 +16657,7 @@
         <v>19946.548602999999</v>
       </c>
     </row>
-    <row r="704" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A704" s="3">
         <v>45991</v>
       </c>
@@ -16685,7 +16680,7 @@
         <v>20011.590204</v>
       </c>
     </row>
-    <row r="705" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A705" s="3">
         <v>45991</v>
       </c>
@@ -16708,7 +16703,7 @@
         <v>20959.447799000001</v>
       </c>
     </row>
-    <row r="706" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A706" s="3">
         <v>45991</v>
       </c>
@@ -16731,7 +16726,7 @@
         <v>21864.328227999998</v>
       </c>
     </row>
-    <row r="707" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A707" s="3">
         <v>45991</v>
       </c>
@@ -16754,7 +16749,7 @@
         <v>23574.223600000001</v>
       </c>
     </row>
-    <row r="708" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A708" s="3">
         <v>45991</v>
       </c>
@@ -16777,7 +16772,7 @@
         <v>24239.636675000002</v>
       </c>
     </row>
-    <row r="709" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A709" s="3">
         <v>45991</v>
       </c>
@@ -16800,7 +16795,7 @@
         <v>25664.716102999999</v>
       </c>
     </row>
-    <row r="710" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A710" s="3">
         <v>45991</v>
       </c>
@@ -16823,7 +16818,7 @@
         <v>26707.4656709999</v>
       </c>
     </row>
-    <row r="711" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A711" s="3">
         <v>45991</v>
       </c>
@@ -16846,7 +16841,7 @@
         <v>26017.659341999999</v>
       </c>
     </row>
-    <row r="712" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A712" s="3">
         <v>45991</v>
       </c>
@@ -16869,7 +16864,7 @@
         <v>24567.182381999999</v>
       </c>
     </row>
-    <row r="713" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A713" s="3">
         <v>45991</v>
       </c>
@@ -16892,7 +16887,7 @@
         <v>23668.661766000001</v>
       </c>
     </row>
-    <row r="714" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A714" s="3">
         <v>45991</v>
       </c>
@@ -16915,7 +16910,7 @@
         <v>23326.015163</v>
       </c>
     </row>
-    <row r="715" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A715" s="3">
         <v>45991</v>
       </c>
@@ -16938,7 +16933,7 @@
         <v>24752.464542000002</v>
       </c>
     </row>
-    <row r="716" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A716" s="3">
         <v>45991</v>
       </c>
@@ -16961,7 +16956,7 @@
         <v>26561.193351999998</v>
       </c>
     </row>
-    <row r="717" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A717" s="3">
         <v>45991</v>
       </c>
@@ -16984,7 +16979,7 @@
         <v>26239.969556</v>
       </c>
     </row>
-    <row r="718" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A718" s="3">
         <v>45991</v>
       </c>
@@ -17007,7 +17002,7 @@
         <v>25987.116069</v>
       </c>
     </row>
-    <row r="719" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A719" s="3">
         <v>45991</v>
       </c>
@@ -17030,7 +17025,7 @@
         <v>25348.237834</v>
       </c>
     </row>
-    <row r="720" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A720" s="3">
         <v>45991</v>
       </c>
@@ -17053,7 +17048,7 @@
         <v>24809.212953999999</v>
       </c>
     </row>
-    <row r="721" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A721" s="3">
         <v>45991</v>
       </c>
@@ -17076,7 +17071,7 @@
         <v>23674.722229999999</v>
       </c>
     </row>
-    <row r="722" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A722" s="3">
         <v>45991</v>
       </c>
@@ -17099,7 +17094,7 @@
         <v>22495.714380000001</v>
       </c>
     </row>
-    <row r="724" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A724" s="7" t="s">
         <v>7</v>
       </c>
@@ -17114,6 +17109,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -17122,140 +17123,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=14.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=14.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=14.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=14.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>ItemUpdatedEventHandlerForConceptSearch</Name>
-    <Synchronization>Asynchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>10001</SequenceNumber>
-    <Url/>
-    <Assembly>conceptSearching.Sharepoint.ContentTypes2010, Version=1.0.0.0, Culture=neutral, PublicKeyToken=858f8f13980e4745</Assembly>
-    <Class>conceptSearching.Sharepoint.ContentTypes2010.CSHandleEvent</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>ItemUpdatingEventHandlerForConceptSearch</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>2</Type>
-    <SequenceNumber>10001</SequenceNumber>
-    <Url/>
-    <Assembly>conceptSearching.Sharepoint.ContentTypes2010, Version=1.0.0.0, Culture=neutral, PublicKeyToken=858f8f13980e4745</Assembly>
-    <Class>conceptSearching.Sharepoint.ContentTypes2010.CSHandleEvent</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>ItemCheckedInEventHandlerForConceptSearch</Name>
-    <Synchronization>Asynchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>10002</SequenceNumber>
-    <Url/>
-    <Assembly>conceptSearching.Sharepoint.ContentTypes2010, Version=1.0.0.0, Culture=neutral, PublicKeyToken=858f8f13980e4745</Assembly>
-    <Class>conceptSearching.Sharepoint.ContentTypes2010.CSHandleEvent</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>ItemUncheckedOutEventHandlerForConceptSearch</Name>
-    <Synchronization>Asynchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>10003</SequenceNumber>
-    <Url/>
-    <Assembly>conceptSearching.Sharepoint.ContentTypes2010, Version=1.0.0.0, Culture=neutral, PublicKeyToken=858f8f13980e4745</Assembly>
-    <Class>conceptSearching.Sharepoint.ContentTypes2010.CSHandleEvent</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>ItemAddedEventHandlerForConceptSearch</Name>
-    <Synchronization>Asynchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>10004</SequenceNumber>
-    <Url/>
-    <Assembly>conceptSearching.Sharepoint.ContentTypes2010, Version=1.0.0.0, Culture=neutral, PublicKeyToken=858f8f13980e4745</Assembly>
-    <Class>conceptSearching.Sharepoint.ContentTypes2010.CSHandleEvent</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>ItemFileMovedEventHandlerForConceptSearch</Name>
-    <Synchronization>Asynchronous</Synchronization>
-    <Type>10009</Type>
-    <SequenceNumber>10005</SequenceNumber>
-    <Url/>
-    <Assembly>conceptSearching.Sharepoint.ContentTypes2010, Version=1.0.0.0, Culture=neutral, PublicKeyToken=858f8f13980e4745</Assembly>
-    <Class>conceptSearching.Sharepoint.ContentTypes2010.CSHandleEvent</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>ItemDeletedEventHandlerForConceptSearch</Name>
-    <Synchronization>Asynchronous</Synchronization>
-    <Type>10003</Type>
-    <SequenceNumber>10006</SequenceNumber>
-    <Url/>
-    <Assembly>conceptSearching.Sharepoint.ContentTypes2010, Version=1.0.0.0, Culture=neutral, PublicKeyToken=858f8f13980e4745</Assembly>
-    <Class>conceptSearching.Sharepoint.ContentTypes2010.CSHandleEvent</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100776092249CC62C48AA17033F357BFB4B" ma:contentTypeVersion="0" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e4ef72e93eae50309b7f5937c6680dd2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="32087e9263820ce1bb09bdcb20175224">
     <xsd:element name="properties">
@@ -17370,14 +17238,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7048AD2F-A120-4F92-B8B4-50D722368C95}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF84784E-56B2-46F5-B48A-7785015432C7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -17395,14 +17255,26 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B011296-3E23-46F6-B017-D87F8598EB34}">
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7048AD2F-A120-4F92-B8B4-50D722368C95}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E74EBBDD-14F1-4BB5-BE12-836D6F909ED6}"/>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E74EBBDD-14F1-4BB5-BE12-836D6F909ED6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>